--- a/results/05_transient_transcription_output/501/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/501/Midpoint_Excel_with_OCR_Results.xlsx
@@ -626,13 +626,14 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5698
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>335</t>
+          <t xml:space="preserve">35
+</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -649,27 +650,30 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>438</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L4" s="2" t="n"/>
@@ -683,25 +687,26 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">43
+</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -712,7 +717,7 @@
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2468
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -724,7 +729,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -736,13 +741,13 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
@@ -758,7 +763,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">326
@@ -767,7 +777,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -779,7 +789,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -792,8 +802,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>442</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -808,15 +817,10 @@
 </t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -834,7 +838,7 @@
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
@@ -846,7 +850,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
@@ -858,8 +862,7 @@
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">088
-</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -870,8 +873,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
@@ -882,14 +884,12 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>808</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -906,12 +906,13 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>08561435132</t>
+          <t xml:space="preserve">548
+</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">339
+          <t xml:space="preserve">3321
 </t>
         </is>
       </c>
@@ -921,10 +922,15 @@
 </t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2319
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -948,7 +954,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">060
 </t>
         </is>
       </c>
@@ -960,25 +966,24 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">400
-</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
@@ -996,7 +1001,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -1020,13 +1025,13 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t xml:space="preserve">135
+</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>611</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
@@ -1054,18 +1059,18 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5836
+          <t xml:space="preserve">536
 </t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>352</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -1083,7 +1088,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1101,7 +1106,8 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1112,19 +1118,18 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">350
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -1136,14 +1141,13 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">347
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1160,8 +1164,7 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1178,19 +1181,20 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">152
+3
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1210,38 +1214,38 @@
           <t>425</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">344
-</t>
-        </is>
-      </c>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">034
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">02
@@ -1250,30 +1254,31 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11108
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">365
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>262</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1422
 </t>
         </is>
       </c>
@@ -1291,7 +1296,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -1309,7 +1314,8 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1320,13 +1326,13 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>261</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1347,29 +1353,38 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2660
-</t>
-        </is>
-      </c>
+      <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t xml:space="preserve">1697
+</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>614</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
+          <t xml:space="preserve">533
+</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2212
+17144
+</t>
+        </is>
+      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">442
@@ -1384,26 +1399,28 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">671
-</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1838
+          <t xml:space="preserve">1839
 </t>
         </is>
       </c>
@@ -1415,20 +1432,23 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650
-</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
-</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">559
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
@@ -1440,33 +1460,29 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">389
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1062
-</t>
-        </is>
-      </c>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="n"/>
       <c r="AA9" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1481,17 +1497,19 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t xml:space="preserve">812
+</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1503,13 +1521,13 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">391
+</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1520,39 +1538,36 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t xml:space="preserve">65
+</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">7 8
 </t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366
-</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t xml:space="preserve">366
+</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">330
@@ -1567,7 +1582,8 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t xml:space="preserve">55
+</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1584,34 +1600,24 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="Y10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1502
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="n"/>
       <c r="AA10" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1626,7 +1632,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4279
+          <t xml:space="preserve">4229
 </t>
         </is>
       </c>
@@ -1644,23 +1650,25 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>421</t>
+          <t xml:space="preserve">832
+</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">45
+</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1669,7 +1677,12 @@
 </t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">182
@@ -1678,7 +1691,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -1690,12 +1703,13 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t xml:space="preserve">130
+</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1705,22 +1719,27 @@
 </t>
         </is>
       </c>
-      <c r="R11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
@@ -1732,23 +1751,29 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1023
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="n"/>
+          <t xml:space="preserve">460
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117177
+38
+</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>6</t>
@@ -1763,22 +1788,15 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 6
-</t>
+          <t>2261</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 317
-</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">217
@@ -1787,19 +1805,19 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">148
+</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1810,7 +1828,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -1822,13 +1840,13 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -1840,25 +1858,23 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3108
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>44</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -1869,38 +1885,34 @@
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>048</t>
+          <t>054</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="Z12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="n"/>
       <c r="AA12" t="inlineStr">
         <is>
           <t>7</t>
@@ -1915,20 +1927,18 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6013
+          <t xml:space="preserve">613
 </t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">343
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>454</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1945,7 +1955,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -1975,13 +1985,13 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -1993,7 +2003,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">396
 </t>
         </is>
       </c>
@@ -2005,7 +2015,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">1838
 </t>
         </is>
       </c>
@@ -2023,20 +2033,18 @@
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">440
-</t>
+          <t>446</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
@@ -2066,8 +2074,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
-</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2078,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -2088,116 +2095,112 @@
 </t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4044</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95
+21
+</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95
+</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">144
 </t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">080
-</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2018
-</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">495
-</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">303
+</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1689
+</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">144
 </t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3803
-</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1145
-</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">360
-</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">270
-</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t xml:space="preserve">92
+</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>61</t>
         </is>
       </c>
       <c r="Z14" s="2" t="n"/>
@@ -2225,19 +2228,18 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -2260,7 +2262,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -2272,13 +2274,13 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -2302,14 +2304,13 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
@@ -2326,7 +2327,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -2350,7 +2351,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -2368,25 +2369,25 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95721
+          <t xml:space="preserve">95771
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11896
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t xml:space="preserve">1182
+</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2397,61 +2398,68 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">6842225
+110
 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">353
+</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">362
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">622
 </t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1547
+          <t xml:space="preserve">542
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>236</t>
+          <t xml:space="preserve">36
+</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2462,11 +2470,16 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr"/>
+          <t xml:space="preserve">8280
+</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1315
@@ -2475,25 +2488,27 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">483
+          <t xml:space="preserve">242
+248174
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1458
+          <t xml:space="preserve">222222
+1117173
 </t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -2511,19 +2526,19 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -2535,38 +2550,38 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2582,65 +2597,62 @@
 </t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
+      <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>863</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">483
+</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t xml:space="preserve">1488
+</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">849
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -2664,36 +2676,42 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">3249
 </t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 7
-</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>434</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">80
+</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">148
+</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2710,30 +2728,29 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">2849
 </t>
         </is>
       </c>
@@ -2744,19 +2761,19 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">1551
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">376
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -2768,25 +2785,23 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -2804,8 +2819,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3264
-</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2814,7 +2828,12 @@
 </t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">229
@@ -2823,26 +2842,23 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">26
@@ -2857,35 +2873,36 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">19
+</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
+          <t xml:space="preserve">6085
 </t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t xml:space="preserve">320
+</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -2903,7 +2920,7 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -2915,22 +2932,28 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">84
+</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="Z19" s="2" t="n"/>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2472
+</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>12</t>
@@ -2943,24 +2966,32 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3905
+</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">313
+</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>443</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2971,7 +3002,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -2983,8 +3014,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2995,37 +3025,33 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">50
+</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t xml:space="preserve">146
+</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -3036,36 +3062,40 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">414
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1124
-</t>
-        </is>
-      </c>
-      <c r="X20" s="2" t="inlineStr"/>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="n"/>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67
+</t>
+        </is>
+      </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
-        </is>
-      </c>
-      <c r="Z20" s="2" t="n"/>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+12
+</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>13</t>
@@ -3080,109 +3110,111 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5429
-</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n"/>
+          <t xml:space="preserve">5422
+</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2211
+23
+</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
+15
+</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4920
+</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">307
+</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4920
-</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283
-</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>76</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>366</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -3199,18 +3231,20 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">87
+</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">2
+</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3227,75 +3261,65 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
+          <t>5363</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">164
 </t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">133
-</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">76
-</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1128
-</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
-      </c>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -3307,13 +3331,14 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">145
+</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -3324,19 +3349,20 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t xml:space="preserve">220
+</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3347,14 +3373,13 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Z22" s="2" t="n"/>
@@ -3372,36 +3397,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25475
-</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">318
+</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>466</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">5555
+57
 </t>
         </is>
       </c>
@@ -3417,43 +3438,49 @@
 </t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8875
+442
+735
+</t>
+        </is>
+      </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">91
+</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">424224514
+17119491
 </t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">45
+</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2720
-</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">313
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="n"/>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t xml:space="preserve">35
+</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -3470,13 +3497,13 @@
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">18722
 </t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -3488,17 +3515,22 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
-</t>
-        </is>
-      </c>
-      <c r="Z23" s="2" t="n"/>
+          <t>963</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77927
+17971
+</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3513,7 +3545,8 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>50321</t>
+          <t xml:space="preserve">603
+</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3524,54 +3557,55 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
+          <t xml:space="preserve">4171
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">620
+</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
@@ -3583,30 +3617,32 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">546
 </t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t xml:space="preserve">83
+</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1544
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t xml:space="preserve">23
+</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
@@ -3617,7 +3653,7 @@
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1872
+          <t xml:space="preserve">374
 </t>
         </is>
       </c>
@@ -3635,19 +3671,20 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t xml:space="preserve">23
+</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3662,21 +3699,24 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>5092</t>
+        </is>
+      </c>
       <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n"/>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1784
+</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">122
@@ -3689,30 +3729,42 @@
       <c r="L25" s="2" t="n"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="n"/>
       <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="n"/>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t xml:space="preserve">5
+</t>
         </is>
       </c>
       <c r="R25" s="2" t="n"/>
       <c r="S25" s="2" t="n"/>
       <c r="T25" s="2" t="inlineStr"/>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>888</t>
-        </is>
-      </c>
+      <c r="U25" s="2" t="n"/>
       <c r="V25" s="2" t="n"/>
-      <c r="W25" s="2" t="n"/>
-      <c r="X25" s="2" t="n"/>
-      <c r="Y25" s="2" t="n"/>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
       <c r="Z25" s="2" t="n"/>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3728,44 +3780,56 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">4555
 </t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2448
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2422222
+1741132
+</t>
+        </is>
+      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">61
+</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3777,13 +3841,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -3795,7 +3858,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -3807,14 +3870,13 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3823,10 +3885,14 @@
 </t>
         </is>
       </c>
-      <c r="U26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>3388</t>
+        </is>
+      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 6 11558
+          <t xml:space="preserve">177 7
 </t>
         </is>
       </c>
@@ -3844,8 +3910,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">455
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Z26" s="2" t="n"/>
@@ -3869,42 +3934,50 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="n"/>
-      <c r="K27" s="2" t="inlineStr"/>
+          <t xml:space="preserve">723
+</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
+</t>
+        </is>
+      </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">159
@@ -3919,13 +3992,13 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">020
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
@@ -3949,7 +4022,7 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -3961,7 +4034,8 @@
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>328234</t>
+          <t xml:space="preserve">334
+</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -3972,17 +4046,20 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">466
+7
 </t>
         </is>
       </c>
@@ -4001,14 +4078,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5501
-</t>
+          <t>55211</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>345</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -4019,66 +4094,67 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">166
+</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">416
 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16816
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">108
 </t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13220
+          <t xml:space="preserve">520
 </t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -4096,49 +4172,36 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>443</t>
-        </is>
-      </c>
-      <c r="X28" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="Y28" s="2" t="inlineStr">
-        <is>
-          <t>2644</t>
-        </is>
-      </c>
-      <c r="Z28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="n"/>
+      <c r="Y28" s="2" t="n"/>
+      <c r="Z28" s="2" t="n"/>
       <c r="AA28" t="inlineStr">
         <is>
           <t>19</t>
@@ -4153,13 +4216,13 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6210
-</t>
+          <t>68111</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>332</t>
+          <t xml:space="preserve">32
+</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -4176,8 +4239,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -4188,19 +4250,19 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -4218,19 +4280,19 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
+          <t xml:space="preserve">4280
 </t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -4242,43 +4304,49 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="n"/>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t xml:space="preserve">27
+</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>126</t>
+          <t xml:space="preserve">8 6
+</t>
         </is>
       </c>
       <c r="Z29" s="2" t="n"/>
@@ -4296,7 +4364,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6249
+          <t xml:space="preserve">629
 </t>
         </is>
       </c>
@@ -4314,35 +4382,37 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4354,18 +4424,19 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">723
+</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
@@ -4377,26 +4448,37 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
-</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr"/>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr"/>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41
+</t>
+        </is>
+      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -4431,52 +4513,53 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15616
-</t>
-        </is>
-      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">370
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">358
+          <t xml:space="preserve">558
 </t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">19
+8
 </t>
         </is>
       </c>
@@ -4494,19 +4577,18 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t xml:space="preserve">43
+</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2329
-</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
-</t>
+          <t>513</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4517,24 +4599,25 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">312
+</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">7296
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11941
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -4552,12 +4635,23 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
-        </is>
-      </c>
-      <c r="Y31" s="2" t="n"/>
-      <c r="Z31" s="2" t="n"/>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1263
+</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9251
+246
+</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -4572,7 +4666,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2364
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
@@ -4584,29 +4678,26 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>5224</t>
-        </is>
-      </c>
+          <t xml:space="preserve">821
+</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -4625,13 +4716,14 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">111
+8
 </t>
         </is>
       </c>
@@ -4643,7 +4735,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -4655,17 +4747,22 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1484
 </t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">6
+</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">388
@@ -4686,22 +4783,17 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">824
 </t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="Z32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="n"/>
       <c r="AA32" t="inlineStr">
         <is>
           <t>21</t>
@@ -4716,66 +4808,67 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">6111
 </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">338
-</t>
+          <t>338</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">92
+</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">132
+</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr"/>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -4799,46 +4892,48 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">141
+</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>424</t>
+          <t xml:space="preserve">44
+</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">285
+</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t xml:space="preserve">182
+</t>
         </is>
       </c>
       <c r="Z33" s="2" t="n"/>
@@ -4854,7 +4949,12 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">487
+</t>
+        </is>
+      </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">312
@@ -4869,19 +4969,20 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -4892,7 +4993,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -4910,7 +5011,8 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4921,34 +5023,27 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1418
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1847
-</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr"/>
       <c r="T34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">303
@@ -4957,8 +5052,7 @@
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4969,19 +5063,21 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t xml:space="preserve">15282985
+122 4
+</t>
         </is>
       </c>
       <c r="Z34" s="2" t="n"/>
@@ -5005,36 +5101,35 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>321</t>
+          <t xml:space="preserve">208
+</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0856
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>433</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -5052,16 +5147,22 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">522
@@ -5082,25 +5183,25 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">134
+</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">550
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -5111,28 +5212,22 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="X35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">22
+122
+</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr"/>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="Z35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2
+7177
+268
+2 24
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="n"/>
       <c r="AA35" t="inlineStr">
         <is>
           <t>24</t>
@@ -5147,7 +5242,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4379
+          <t xml:space="preserve">4339
 </t>
         </is>
       </c>
@@ -5159,13 +5254,14 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">220
+171
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -5177,7 +5273,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -5189,14 +5285,13 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
-</t>
+          <t>482</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -5207,31 +5302,31 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">740
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
@@ -5255,7 +5350,7 @@
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
@@ -5267,19 +5362,21 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">7777277
+22
+117981
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">77727
+32
 </t>
         </is>
       </c>
@@ -5296,12 +5393,7 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2222
-</t>
-        </is>
-      </c>
+      <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">255
@@ -5310,62 +5402,62 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">6224
 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -5383,43 +5475,38 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
-</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">341
+</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="Z37" s="2" t="n"/>
@@ -5435,7 +5522,12 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22116
+</t>
+        </is>
+      </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1516
@@ -5444,25 +5536,25 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -5472,28 +5564,32 @@
 </t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">1
+12
 </t>
         </is>
       </c>
@@ -5505,62 +5601,62 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3898
+          <t xml:space="preserve">595
 </t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>832</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">478
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1510
+          <t xml:space="preserve">1816
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1141
-</t>
-        </is>
-      </c>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr"/>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t xml:space="preserve">71793
+</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
-</t>
-        </is>
-      </c>
-      <c r="Z38" s="2" t="n"/>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -5580,19 +5676,18 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">689
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -5604,7 +5699,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5616,7 +5711,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13010
+          <t xml:space="preserve">3200
 </t>
         </is>
       </c>
@@ -5629,22 +5724,22 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
-</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">879
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">488
+</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr"/>
       <c r="Q39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">267
@@ -5653,7 +5748,7 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -5665,19 +5760,19 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -5689,13 +5784,13 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>84</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5718,7 +5813,8 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>54441</t>
+          <t xml:space="preserve">546
+</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5729,58 +5825,65 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1381
 </t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2821
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>554</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t xml:space="preserve">69
+</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
-</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr"/>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1060004</t>
+          <t xml:space="preserve">102
+</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">72
+</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
@@ -5792,8 +5895,7 @@
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
@@ -5804,31 +5906,30 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8224
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>943</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -5840,13 +5941,13 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3964
+          <t xml:space="preserve">364
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -5864,24 +5965,25 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6171
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>303</t>
+          <t xml:space="preserve">307
+</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -5893,19 +5995,19 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -5916,57 +6018,53 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">360
+</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">88
 </t>
         </is>
       </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300
-</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1150
-</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
+      <c r="T41" s="2" t="n"/>
       <c r="U41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">342
@@ -5981,25 +6079,19 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="X41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr"/>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">2410
 </t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -6017,23 +6109,26 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">5875
 </t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t xml:space="preserve">314
+</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>462</t>
+          <t xml:space="preserve">147
+4
+</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -6045,7 +6140,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -6057,13 +6152,13 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
@@ -6075,25 +6170,25 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6105,7 +6200,8 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">155
+</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -6116,19 +6212,19 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -6140,19 +6236,14 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="Y42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8289
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr"/>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2236
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -6170,36 +6261,36 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3240
+          <t xml:space="preserve">4811
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>319</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1530
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
@@ -6217,8 +6308,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -6229,36 +6319,38 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t xml:space="preserve">264
+</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
@@ -6275,37 +6367,36 @@
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1998
 </t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">521
 </t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1655
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -6323,19 +6414,18 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580
+          <t xml:space="preserve">540
 </t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -6347,55 +6437,52 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">1797
 </t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">985
 </t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">5915
 </t>
         </is>
       </c>
@@ -6413,12 +6500,13 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">142
+</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">8858
 </t>
         </is>
       </c>
@@ -6430,36 +6518,37 @@
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">227
+</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">2853
 </t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">424
 </t>
         </is>
       </c>
@@ -6477,40 +6566,29 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
-</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">157
 </t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
+      <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">61
@@ -6519,7 +6597,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -6531,25 +6609,25 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>466</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">46
+</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -6560,31 +6638,31 @@
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1844
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>563</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
@@ -6601,17 +6679,21 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="2" t="inlineStr"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -6626,127 +6708,130 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518
+          <t xml:space="preserve">31213
 </t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1857
+          <t xml:space="preserve">1877
 </t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11399
-</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
+          <t xml:space="preserve">23212
+</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3560
-</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">523
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1224
+</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">1011
 </t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0609
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">187
+</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2265
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">584
 </t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1790
+          <t xml:space="preserve">736
 </t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8818
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">828
+</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t xml:space="preserve">1364
+</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>72</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t xml:space="preserve">14402
+</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1865
+          <t xml:space="preserve">8685
 </t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1841
+          <t xml:space="preserve">6478
 </t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
-        </is>
-      </c>
-      <c r="Z46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="n"/>
       <c r="AA46" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -6759,46 +6844,45 @@
           <t>Tot.</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">518
+</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">15838
 </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1053
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1211
-</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -6809,42 +6893,45 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t xml:space="preserve">494
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>920</t>
+          <t xml:space="preserve">392
+</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -6855,7 +6942,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -6865,13 +6952,13 @@
 </t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>Tot.</t>

--- a/results/05_transient_transcription_output/501/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/501/Midpoint_Excel_with_OCR_Results.xlsx
@@ -626,59 +626,54 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">15698
 </t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1728
 </t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t xml:space="preserve">138
+</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">355
@@ -693,19 +688,19 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">2383
 </t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -715,42 +710,12 @@
 </t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">418
-</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">322
-</t>
-        </is>
-      </c>
+      <c r="U4" s="2" t="n"/>
+      <c r="V4" s="2" t="n"/>
+      <c r="W4" s="2" t="n"/>
+      <c r="X4" s="2" t="n"/>
+      <c r="Y4" s="2" t="n"/>
+      <c r="Z4" s="2" t="n"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1</t>
@@ -765,7 +730,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">5127
 </t>
         </is>
       </c>
@@ -777,26 +742,30 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2218
+</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -817,10 +786,15 @@
 </t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1655
+</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -832,64 +806,63 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
-</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="n"/>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t xml:space="preserve">1468
+</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1284
 </t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">1103
+</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">268
+</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t xml:space="preserve">322
+</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -906,13 +879,13 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
+          <t xml:space="preserve">15048
 </t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3321
+          <t xml:space="preserve">3348
 </t>
         </is>
       </c>
@@ -924,20 +897,19 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1206231
 </t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -954,7 +926,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">060
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -966,82 +938,80 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1898
 </t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11400
+</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="n"/>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">1327
 </t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1152
 </t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">424
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t xml:space="preserve">81
+</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t xml:space="preserve">2012
+</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">2302
 </t>
         </is>
       </c>
@@ -1059,54 +1029,53 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536
+          <t xml:space="preserve">5836
 </t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>353</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">1231
 </t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>461</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">0080
 </t>
         </is>
       </c>
@@ -1118,19 +1087,13 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
-      </c>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1141,30 +1104,32 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">397
+          <t xml:space="preserve">347
 </t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t xml:space="preserve">1138
+</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>241</t>
+          <t xml:space="preserve">217
+</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1175,26 +1140,26 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-3
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t xml:space="preserve">334
+</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1211,38 +1176,38 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>425</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n"/>
+          <t xml:space="preserve">4851
+</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">344
+</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11510
 </t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1227
+</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1910
 </t>
         </is>
       </c>
@@ -1254,31 +1219,26 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">71108
+</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">2365
 </t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1422
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -1290,49 +1250,48 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">1151
 </t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">1710
 </t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">422
+          <t xml:space="preserve">9422
 </t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>451</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">1117
 </t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>261</t>
+          <t xml:space="preserve">867
+</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1353,135 +1312,128 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26360
+</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1697
+          <t xml:space="preserve">11697
 </t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">533
-</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2212
-17144
+          <t xml:space="preserve">391
 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
+          <t xml:space="preserve">16442
 </t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
+          <t xml:space="preserve">1684
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">2587
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1839
+          <t xml:space="preserve">11830
 </t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">497
+          <t xml:space="preserve">9497
 </t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t xml:space="preserve">11690
+</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">718
+</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">1277
 </t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2241
+          <t xml:space="preserve">12241
 </t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">11397
 </t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">1696
 </t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">389
-</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">289
+</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="n"/>
       <c r="Z9" s="2" t="n"/>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1497,19 +1449,18 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">2312
 </t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
@@ -1521,71 +1472,76 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">1232
+</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1134
+</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2366
+</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">330
+</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">88
 </t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">37
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7 8
-</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">366
-</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">330
-</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">112
@@ -1594,30 +1550,40 @@
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">448
+          <t xml:space="preserve">1448
 </t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="Y10" s="2" t="inlineStr"/>
-      <c r="Z10" s="2" t="n"/>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300
+</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1632,57 +1598,44 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4229
+          <t xml:space="preserve">14278
 </t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
-</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">300
+</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">182
@@ -1691,89 +1644,63 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">9289
 </t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">11489
 </t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">1310
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="X11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">460
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117177
-38
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1217
+</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="n"/>
+      <c r="X11" s="2" t="n"/>
+      <c r="Y11" s="2" t="n"/>
+      <c r="Z11" s="2" t="n"/>
       <c r="AA11" t="inlineStr">
         <is>
           <t>6</t>
@@ -1788,47 +1715,49 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2261</t>
+          <t xml:space="preserve">20 6 1
+</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>513</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
+          <t xml:space="preserve">317
+</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">1287
 </t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -1846,35 +1775,37 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
+          <t xml:space="preserve">1530
 </t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">3118
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">144
+</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t xml:space="preserve">162
+</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -1885,34 +1816,39 @@
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">1840
 </t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>054</t>
+          <t xml:space="preserve">1023
+</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="Z12" s="2" t="n"/>
+          <t xml:space="preserve">470
+</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>7</t>
@@ -1927,23 +1863,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">613
+          <t xml:space="preserve">16013
 </t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>343</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>454</t>
+          <t xml:space="preserve">1154
+</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
@@ -1955,7 +1892,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
@@ -1967,13 +1904,13 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">1157
 </t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -1989,77 +1926,77 @@
 </t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
+      <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">12490
 </t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">396
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
+          <t xml:space="preserve">8332
 </t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1838
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>446</t>
+          <t xml:space="preserve">1440
+</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>145</t>
+          <t xml:space="preserve">151
+</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="Z13" s="2" t="n"/>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12654
+</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>8</t>
@@ -2074,7 +2011,8 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4371</t>
+          <t xml:space="preserve">14880
+</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2085,20 +2023,26 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1246
+</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4044</t>
+          <t xml:space="preserve">1136
+</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2059,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -2127,83 +2071,67 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">95
-21
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1120
+</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">1490
 </t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2303
+</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="n"/>
+      <c r="S14" s="2" t="n"/>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1689
-</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2360
+</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="n"/>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="Z14" s="2" t="n"/>
+          <t xml:space="preserve">0208
+</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4312
+</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>9</t>
@@ -2218,7 +2146,8 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5524</t>
+          <t xml:space="preserve">18329
+</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2228,29 +2157,31 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1020
 </t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">1231
+</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t xml:space="preserve">102
+</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -2262,37 +2193,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">008
 </t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
@@ -2302,35 +2228,21 @@
 </t>
         </is>
       </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
+      <c r="R15" s="2" t="n"/>
+      <c r="S15" s="2" t="n"/>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">1154
 </t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
-</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">3820
+</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="n"/>
       <c r="W15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">140
@@ -2339,20 +2251,19 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2369,78 +2280,73 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95771
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t xml:space="preserve">12916
+</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">27268
 </t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>821</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6842225
-110
+          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">353
+          <t xml:space="preserve">973
 </t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t xml:space="preserve">562
+</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">1899
 </t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">29529
+</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">22120
 </t>
         </is>
       </c>
@@ -2452,13 +2358,13 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">542
+          <t xml:space="preserve">11547
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">10836
 </t>
         </is>
       </c>
@@ -2470,45 +2376,43 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8280
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">11882
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1315
+          <t xml:space="preserve">11310
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-248174
+          <t xml:space="preserve">1483
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222222
-1117173
+          <t xml:space="preserve">112458
 </t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">11244
 </t>
         </is>
       </c>
@@ -2526,110 +2430,109 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">3154
 </t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">1236
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="n"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
-</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr"/>
+          <t xml:space="preserve">9425
+</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">1873
+</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">376
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t xml:space="preserve">263
+</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2640,22 +2543,17 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">483
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1488
-</t>
-        </is>
-      </c>
-      <c r="Z17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2292
+</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="n"/>
       <c r="AA17" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2670,48 +2568,48 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521
+          <t xml:space="preserve">5321
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3249
+          <t xml:space="preserve">029
 </t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t xml:space="preserve">227
+</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>164</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2722,86 +2620,80 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t xml:space="preserve">175
+</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2849
-</t>
+          <t>29111</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t xml:space="preserve">1152
+</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1551
+          <t xml:space="preserve">1155
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1404
+</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="n"/>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">11844
+</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t xml:space="preserve">1220
+</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
@@ -2819,7 +2711,8 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5861</t>
+          <t xml:space="preserve">3264
+</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2830,7 +2723,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1123
 </t>
         </is>
       </c>
@@ -2842,13 +2735,13 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -2858,7 +2751,12 @@
 </t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1926
+</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">26
@@ -2867,31 +2765,22 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1135
+</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6085
+          <t xml:space="preserve">1605
 </t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">160
+</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2908,49 +2797,44 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1414
+</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="n"/>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2472
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -2968,41 +2852,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3905
-</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">313
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t xml:space="preserve">1172
+</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">1141
+</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -3014,34 +2894,38 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr"/>
+          <t xml:space="preserve">5220
+</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">283
@@ -3050,7 +2934,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
@@ -3062,7 +2946,8 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>145</t>
+          <t xml:space="preserve">225
+</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -3073,26 +2958,31 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="n"/>
+          <t xml:space="preserve">1222
+</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11824
+</t>
+        </is>
+      </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">520
+</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-12
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
@@ -3121,72 +3011,67 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1364
 </t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t xml:space="preserve">238
+</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211
-23
-</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1132
+</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">1775
+</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-15
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4920
-</t>
+          <t>420</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
@@ -3204,46 +3089,49 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">1172
+</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>366</t>
+          <t xml:space="preserve">366
+</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -3261,35 +3149,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n"/>
+          <t xml:space="preserve">15363
+</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">152
+</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">12225
 </t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t xml:space="preserve">1166
+</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
@@ -3301,25 +3196,26 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1010
 </t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t xml:space="preserve">1107
+</t>
         </is>
       </c>
       <c r="N22" s="2" t="n"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
@@ -3331,8 +3227,7 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
@@ -3343,25 +3238,25 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">1849
 </t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">2390
 </t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
@@ -3373,16 +3268,22 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z22" s="2" t="n"/>
+          <t xml:space="preserve">2163
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1262
+</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>15</t>
@@ -3397,32 +3298,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n"/>
+          <t xml:space="preserve">2315
+</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1603
+</t>
+        </is>
+      </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">725
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">11171
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t xml:space="preserve">868
+</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5555
-57
+          <t xml:space="preserve">1600
 </t>
         </is>
       </c>
@@ -3434,52 +3340,55 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8875
-442
-735
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">7191
 </t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">424224514
-17119491
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t xml:space="preserve">12120
+</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="n"/>
+          <t xml:space="preserve">1412
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1544
+</t>
+        </is>
+      </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -3491,43 +3400,43 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">1829
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18722
+          <t xml:space="preserve">1872
 </t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">13026
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
+          <t xml:space="preserve">1688
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">1428
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t xml:space="preserve">1273
+</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77927
-17971
+          <t xml:space="preserve">11224
 </t>
         </is>
       </c>
@@ -3545,7 +3454,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">603
+          <t xml:space="preserve">3095
 </t>
         </is>
       </c>
@@ -3557,46 +3466,41 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4171
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1114
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -3605,49 +3509,41 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">546
+          <t xml:space="preserve">046
 </t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1147
 </t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
@@ -3671,19 +3567,19 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3701,71 +3597,135 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n"/>
+          <t xml:space="preserve">4255
+</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2119
+</t>
+        </is>
+      </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>815</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="n"/>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1248
+</t>
+        </is>
+      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1784
+          <t xml:space="preserve">1842
 </t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="n"/>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="n"/>
+          <t xml:space="preserve">1150
+</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1109
+</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="N25" s="2" t="n"/>
-      <c r="O25" s="2" t="n"/>
-      <c r="P25" s="2" t="n"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1400
+</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11140
+</t>
+        </is>
+      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="n"/>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
       <c r="S25" s="2" t="n"/>
-      <c r="T25" s="2" t="inlineStr"/>
-      <c r="U25" s="2" t="n"/>
-      <c r="V25" s="2" t="n"/>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1202
+</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">328
+</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1177
+</t>
+        </is>
+      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="2" t="n"/>
+          <t xml:space="preserve">14575
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11121
+</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>16</t>
@@ -3780,140 +3740,136 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4555
+          <t xml:space="preserve">5304
 </t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">2225
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1116
+</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1159
+</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="n"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1820
+</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">293
+</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">142
 </t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2422222
-1741132
-</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">400
-</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t xml:space="preserve">334
+</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177 7
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="X26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="n"/>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z26" s="2" t="n"/>
+          <t xml:space="preserve">2270
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1250
+</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>17</t>
@@ -3928,142 +3884,125 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304
+          <t xml:space="preserve">5501
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1152
+</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1235
+</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1163
+</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">308
+</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="n"/>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1160
+</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1374
+</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">723
-</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290
-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">95
-</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">620
-</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">293
-</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">334
-</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+      <c r="X27" s="2" t="n"/>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">466
-7
-</t>
-        </is>
-      </c>
-      <c r="Z27" s="2" t="n"/>
+          <t xml:space="preserve">10266
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>18</t>
@@ -4078,130 +4017,146 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>55211</t>
+          <t xml:space="preserve">16210
+</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>345</t>
+          <t xml:space="preserve">332
+</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">416
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
+          <t xml:space="preserve">14280
 </t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">11208
 </t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">321
+</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">434
+</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1277
+</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1133
+</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">308
 </t>
         </is>
       </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="X28" s="2" t="n"/>
-      <c r="Y28" s="2" t="n"/>
-      <c r="Z28" s="2" t="n"/>
       <c r="AA28" t="inlineStr">
         <is>
           <t>19</t>
@@ -4216,118 +4171,114 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>68111</t>
+          <t xml:space="preserve">6249
+</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">344
 </t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1122
 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">1008
 </t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4280
+          <t xml:space="preserve">1413
 </t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">3835
 </t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>456</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>424</t>
-        </is>
-      </c>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">1277
 </t>
         </is>
       </c>
@@ -4339,17 +4290,22 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 6
-</t>
-        </is>
-      </c>
-      <c r="Z29" s="2" t="n"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30682
+</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>20</t>
@@ -4364,142 +4320,132 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">27819
 </t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
+          <t xml:space="preserve">1616
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">7145
 </t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1871
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1570
 </t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">3720
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">1558
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
+          <t xml:space="preserve">1306
 </t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">2223
 </t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">017
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">1531
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">709
+</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="n"/>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">726
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">81941
 </t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1668
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1120
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="n"/>
       <c r="Z30" s="2" t="n"/>
       <c r="AA30" t="inlineStr">
         <is>
@@ -4515,140 +4461,124 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n"/>
+          <t xml:space="preserve">2364
+</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">323
+</t>
+        </is>
+      </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>489</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
-</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1112
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">506
-</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">43
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t xml:space="preserve">465
+</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t xml:space="preserve">103
+</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1551
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">312
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1142
+</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="n"/>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7296
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">388
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
+          <t xml:space="preserve">2293
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9251
-246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -4666,134 +4596,120 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">0111
 </t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">338
 </t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">112321
+</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-8
-</t>
-        </is>
-      </c>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">465
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="n"/>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1484
-</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1141
+</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="n"/>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">388
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="n"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">1283
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="Z32" s="2" t="n"/>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">319
+</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>21</t>
@@ -4808,135 +4724,133 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6111
+          <t xml:space="preserve">4487
 </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>338</t>
+          <t xml:space="preserve">312
+</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">2229
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1167
+</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">1410
 </t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">336
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="n"/>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1147
+</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="n"/>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">303
+</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="n"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">12180
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="Z33" s="2" t="n"/>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>22</t>
@@ -4951,136 +4865,138 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">487
+          <t xml:space="preserve">3866
 </t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1232
+</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">11160
 </t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">129522
 </t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">190
+</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1134
+</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">0250
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">7190
 </t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">1127
 </t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15282985
-122 4
-</t>
-        </is>
-      </c>
-      <c r="Z34" s="2" t="n"/>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>23</t>
@@ -5095,139 +5011,137 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3866
+          <t xml:space="preserve">4339
 </t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1170
+</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">1133
 </t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1285
 </t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">522
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
+          <t xml:space="preserve">2228
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-122
-</t>
-        </is>
-      </c>
-      <c r="X35" s="2" t="inlineStr"/>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">97
+</t>
+        </is>
+      </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-7177
-268
-2 24
-</t>
-        </is>
-      </c>
-      <c r="Z35" s="2" t="n"/>
+          <t xml:space="preserve">18398
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>4221</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>24</t>
@@ -5242,145 +5156,132 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4339
+          <t xml:space="preserve">3413
 </t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-171
-</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1123
+</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
+          <t xml:space="preserve">1940
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t xml:space="preserve">1136
+</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7777277
-22
-117981
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77727
-32
-</t>
-        </is>
-      </c>
-      <c r="Z36" s="2" t="n"/>
+          <t xml:space="preserve">2188
+</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>25</t>
@@ -5393,123 +5294,145 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>9661</t>
+        </is>
+      </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">11816
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">1689
 </t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">11102
 </t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">827
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6224
-</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
+          <t xml:space="preserve">358
+</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1010
+</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">1232
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">12402
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1335
 </t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">17826
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1478
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">341
-</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr"/>
+          <t xml:space="preserve">11410
+</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11342
+</t>
+        </is>
+      </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">9498
+</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="Z37" s="2" t="n"/>
+          <t xml:space="preserve">1812
+</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -5524,136 +5447,131 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22116
+          <t xml:space="preserve">4433
 </t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1516
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>428</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">21112
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-12
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402
+          <t xml:space="preserve">14180
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">595
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t xml:space="preserve">1148
+</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1816
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2269
+</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71793
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">374
 </t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -5671,131 +5589,129 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t xml:space="preserve">3146
+</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t xml:space="preserve">1292
+</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">1142
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>512</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3200
-</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr"/>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11102
+</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
-</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr"/>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="n"/>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1224
+</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="n"/>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">3964
+</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">2266
 </t>
         </is>
       </c>
@@ -5813,77 +5729,77 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">546
+          <t xml:space="preserve">6171
 </t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1381
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">1262217
 </t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">1160
+</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t xml:space="preserve">1086
+</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
@@ -5895,59 +5811,55 @@
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t xml:space="preserve">300
+</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>943</t>
-        </is>
-      </c>
+          <t xml:space="preserve">7942
+</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="n"/>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1847
 </t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
+          <t xml:space="preserve">81206
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">12216
 </t>
         </is>
       </c>
@@ -5965,134 +5877,139 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">5875
 </t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t xml:space="preserve">99
+</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="n"/>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1222
+</t>
+        </is>
+      </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
+          <t xml:space="preserve">2926
 </t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1275
 </t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="X41" s="2" t="inlineStr"/>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2410
+          <t xml:space="preserve">1288
 </t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6109,141 +6026,137 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5875
+          <t xml:space="preserve">4811
 </t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-4
+          <t xml:space="preserve">1154
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1233
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1109
+</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="n"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9209
+</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1147
+</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1246
+</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1139
-</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">298
-</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="Y42" s="2" t="inlineStr"/>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1928
+</t>
+        </is>
+      </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -6261,68 +6174,64 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4811
+          <t xml:space="preserve">3540
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>319</t>
+          <t xml:space="preserve">305
+</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">2239
 </t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1041
 </t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">100
+</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">108
@@ -6331,72 +6240,68 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">915
+</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="n"/>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1147
 </t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">2013
 </t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">314
+</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1998
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
+          <t xml:space="preserve">19253
 </t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">2461
 </t>
         </is>
       </c>
@@ -6414,141 +6319,134 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">540
+          <t xml:space="preserve">2380
 </t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>303</t>
+          <t xml:space="preserve">307
+</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>344</t>
-        </is>
-      </c>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t xml:space="preserve">6561
+</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1909
+</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1797
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5915
+          <t xml:space="preserve">1440
 </t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8858
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1093
 </t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">1147
 </t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">1122
 </t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2853
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">424
+          <t xml:space="preserve">1824
 </t>
         </is>
       </c>
@@ -6566,131 +6464,139 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t xml:space="preserve">331029
+</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">118715
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1919
+</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11221
+</t>
+        </is>
+      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr"/>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">822246
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">15123
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">18222
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t xml:space="preserve">1110111
+</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18159
+</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">112265
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">10218
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1838
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">18369
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t xml:space="preserve">88886
+</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">214621
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1061
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t xml:space="preserve">10987
+</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">12228
 </t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">11172
 </t>
         </is>
       </c>
@@ -6708,130 +6614,126 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31213
+          <t xml:space="preserve">5518
 </t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1877
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23212
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr"/>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1121
+</t>
+        </is>
+      </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr"/>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1224
-</t>
-        </is>
-      </c>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1011
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1108
+</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">1494
 </t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">584
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">736
+          <t xml:space="preserve">1288
 </t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1364
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14402
-</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8685
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">3908
+</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="n"/>
+      <c r="W46" s="2" t="n"/>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6478
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>431</t>
-        </is>
-      </c>
-      <c r="Z46" s="2" t="n"/>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1196
+</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -6842,121 +6744,6 @@
       <c r="B47" t="inlineStr">
         <is>
           <t>Tot.</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">518
-</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15838
-</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">94
-</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">392
-</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">308
-</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">

--- a/results/05_transient_transcription_output/501/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/501/Midpoint_Excel_with_OCR_Results.xlsx
@@ -626,19 +626,25 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15698
+          <t xml:space="preserve">5628
 </t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
+          <t xml:space="preserve">835
+</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">97
+</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -648,10 +654,15 @@
 </t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -663,20 +674,31 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">355
+          <t xml:space="preserve">345
 </t>
         </is>
       </c>
@@ -688,7 +710,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2383
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
@@ -700,7 +722,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
@@ -730,7 +752,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5127
+          <t xml:space="preserve">151 27 1
 </t>
         </is>
       </c>
@@ -742,59 +764,61 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2218
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">764
+</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t xml:space="preserve">1129
+</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1655
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -806,7 +830,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -818,7 +842,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">1840
 </t>
         </is>
       </c>
@@ -828,40 +852,44 @@
 </t>
         </is>
       </c>
-      <c r="T5" s="2" t="n"/>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>04449</t>
+        </is>
+      </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1468
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">968
 </t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">382
 </t>
         </is>
       </c>
@@ -879,13 +907,13 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15048
+          <t xml:space="preserve">23048
 </t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3348
+          <t xml:space="preserve">339
 </t>
         </is>
       </c>
@@ -903,13 +931,14 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206231
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t xml:space="preserve">75
+</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -926,7 +955,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -938,32 +967,37 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1898
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11400
-</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="n"/>
+          <t xml:space="preserve">21098
+</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1327
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -981,7 +1015,7 @@
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -993,7 +1027,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1642
 </t>
         </is>
       </c>
@@ -1005,13 +1039,13 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2302
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
@@ -1035,7 +1069,8 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t xml:space="preserve">353
+</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1046,13 +1081,13 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -1070,12 +1105,13 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t xml:space="preserve">169
+</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1087,13 +1123,20 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>546</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="n"/>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t xml:space="preserve">350
+</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1104,62 +1147,61 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">347
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">836
 </t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">424
 </t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1176,63 +1218,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4851
+          <t xml:space="preserve">112851
 </t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11510
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
-</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
+          <t xml:space="preserve">2828
+</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">812
+</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910
+          <t xml:space="preserve">0110
 </t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">1161
 </t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71108
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2365
+          <t xml:space="preserve">360
 </t>
         </is>
       </c>
@@ -1256,24 +1309,26 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1710
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">143
+</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422
+          <t xml:space="preserve">422
 </t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">2019
+</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1282,24 +1337,9 @@
 </t>
         </is>
       </c>
-      <c r="X8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1117
-</t>
-        </is>
-      </c>
-      <c r="Y8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">867
-</t>
-        </is>
-      </c>
-      <c r="Z8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
+      <c r="X8" s="2" t="n"/>
+      <c r="Y8" s="2" t="n"/>
+      <c r="Z8" s="2" t="n"/>
       <c r="AA8" t="inlineStr">
         <is>
           <t>5</t>
@@ -1314,13 +1354,13 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26360
+          <t xml:space="preserve">26660
 </t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11697
+          <t xml:space="preserve">1697
 </t>
         </is>
       </c>
@@ -1330,7 +1370,12 @@
 </t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14134
+</t>
+        </is>
+      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1164
@@ -1339,55 +1384,61 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
+          <t xml:space="preserve">3291
 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16442
+          <t xml:space="preserve">6142
 </t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1684
+          <t xml:space="preserve">684
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">671
+</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">329
+</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2587
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11830
+          <t xml:space="preserve">1830
 </t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9497
+          <t xml:space="preserve">487
 </t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11690
+          <t xml:space="preserve">1690
 </t>
         </is>
       </c>
@@ -1399,7 +1450,7 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -1417,7 +1468,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11397
+          <t xml:space="preserve">1397
 </t>
         </is>
       </c>
@@ -1433,8 +1484,18 @@
 </t>
         </is>
       </c>
-      <c r="Y9" s="2" t="n"/>
-      <c r="Z9" s="2" t="n"/>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11862
+</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11584
+</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1455,12 +1516,13 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t xml:space="preserve">229
+</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
+          <t xml:space="preserve">1872
 </t>
         </is>
       </c>
@@ -1472,19 +1534,19 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -1494,34 +1556,29 @@
 </t>
         </is>
       </c>
-      <c r="K10" s="2" t="n"/>
+      <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366
+          <t xml:space="preserve">366
 </t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -1533,12 +1590,13 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">144
+</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -1550,37 +1608,37 @@
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1448
+          <t xml:space="preserve">1948
 </t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -1598,44 +1656,58 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14278
+          <t xml:space="preserve">4279
 </t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
+          <t xml:space="preserve">3080
+</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">139
+</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>06</t>
+          <t xml:space="preserve">1148
+</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr"/>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">182
@@ -1644,11 +1716,11 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="n"/>
+          <t xml:space="preserve">614
+</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1130
@@ -1663,40 +1735,35 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9289
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11489
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">8220
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1310
-</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1217
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">8210
+</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="n"/>
       <c r="W11" s="2" t="n"/>
       <c r="X11" s="2" t="n"/>
       <c r="Y11" s="2" t="n"/>
@@ -1715,24 +1782,24 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20 6 1
+          <t xml:space="preserve">2067
 </t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">517
 </t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1287
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
@@ -1744,20 +1811,25 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="n"/>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61
+</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -1775,54 +1847,55 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1530
+          <t xml:space="preserve">530
 </t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">1100
+</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3118
+          <t xml:space="preserve">3108
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1142
 </t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -1834,19 +1907,20 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1023
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
+          <t xml:space="preserve">12170
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">18358
+</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1863,30 +1937,31 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16013
+          <t xml:space="preserve">6013
 </t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>343</t>
+          <t xml:space="preserve">343
+</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">1594
 </t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
@@ -1904,13 +1979,13 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1157
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1929,72 +2004,73 @@
       <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12490
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8332
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t xml:space="preserve">135
+</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1440
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">1020
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">1151
 </t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">1021
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t xml:space="preserve">088
+</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12654
-</t>
+          <t>865</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2011,7 +2087,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14880
+          <t xml:space="preserve">4890
 </t>
         </is>
       </c>
@@ -2023,25 +2099,25 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -2078,60 +2154,71 @@
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1490
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2303
-</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="n"/>
-      <c r="S14" s="2" t="n"/>
+          <t xml:space="preserve">303
+</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t xml:space="preserve">169
+</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2360
-</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="n"/>
+          <t xml:space="preserve">360
+</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">270
+</t>
+        </is>
+      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0208
-</t>
-        </is>
-      </c>
-      <c r="Z14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4312
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">0808
+</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="n"/>
       <c r="AA14" t="inlineStr">
         <is>
           <t>9</t>
@@ -2146,30 +2233,29 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18329
+          <t xml:space="preserve">2521
 </t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>343</t>
+          <t xml:space="preserve">315
+</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
-</t>
+          <t>933</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
@@ -2181,7 +2267,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -2193,43 +2279,58 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="n"/>
+          <t xml:space="preserve">1104
+</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9
+</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="n"/>
-      <c r="S15" s="2" t="n"/>
+          <t xml:space="preserve">3120
+</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1145
+</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1154
@@ -2238,14 +2339,18 @@
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3820
-</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="n"/>
+          <t xml:space="preserve">38208
+</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
@@ -2255,17 +2360,8 @@
 </t>
         </is>
       </c>
-      <c r="Y15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1234
-</t>
-        </is>
-      </c>
-      <c r="Z15" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
+      <c r="Y15" s="2" t="n"/>
+      <c r="Z15" s="2" t="n"/>
       <c r="AA15" t="inlineStr">
         <is>
           <t>10</t>
@@ -2280,36 +2376,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">2371
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12916
+          <t xml:space="preserve">1823916
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27268
+          <t xml:space="preserve">2168
 </t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t xml:space="preserve">1182
+</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
+          <t xml:space="preserve">618
 </t>
         </is>
       </c>
@@ -2327,23 +2424,28 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1899
+          <t xml:space="preserve">1898
 </t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29529
-</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2028
+</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">22120
@@ -2358,13 +2460,13 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11547
+          <t xml:space="preserve">1547
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10836
+          <t xml:space="preserve">836
 </t>
         </is>
       </c>
@@ -2382,37 +2484,37 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11882
+          <t xml:space="preserve">1882
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11310
+          <t xml:space="preserve">1315
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1728
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1483
+          <t xml:space="preserve">483
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112458
+          <t xml:space="preserve">11438
 </t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11244
+          <t xml:space="preserve">10244
 </t>
         </is>
       </c>
@@ -2436,31 +2538,31 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">3819
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">22316
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -2476,22 +2578,28 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="2" t="n"/>
+      <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="n"/>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9425
+          <t xml:space="preserve">425
 </t>
         </is>
       </c>
@@ -2509,30 +2617,31 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1873
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t xml:space="preserve">1164
+</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">376
+          <t xml:space="preserve">9816
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>9465</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2549,11 +2658,16 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2292
-</t>
-        </is>
-      </c>
-      <c r="Z17" s="2" t="n"/>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2568,25 +2682,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5321
+          <t xml:space="preserve">10321
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">029
+          <t xml:space="preserve">0229
 </t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">827
 </t>
         </is>
       </c>
@@ -2598,18 +2711,18 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2620,7 +2733,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -2630,7 +2743,12 @@
 </t>
         </is>
       </c>
-      <c r="N18" s="2" t="n"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">175
@@ -2639,18 +2757,19 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>29111</t>
+          <t xml:space="preserve">2804
+</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -2662,26 +2781,31 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="n"/>
+          <t xml:space="preserve">404
+</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1081
+</t>
+        </is>
+      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11844
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -2693,7 +2817,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -2711,20 +2835,18 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3264
-</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
+          <t xml:space="preserve">354
 </t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2753,7 +2875,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1926
+          <t xml:space="preserve">11206
 </t>
         </is>
       </c>
@@ -2765,21 +2887,31 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
-</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
+          <t xml:space="preserve">605
 </t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2791,7 +2923,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -2803,17 +2935,22 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1414
-</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="n"/>
+          <t xml:space="preserve">1614
+</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">129
@@ -2828,7 +2965,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -2852,31 +2989,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n"/>
+          <t xml:space="preserve">93905
+</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">9149
 </t>
         </is>
       </c>
@@ -2888,41 +3031,42 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t xml:space="preserve">07
+</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -2934,7 +3078,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -2958,13 +3102,13 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">16202
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11824
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
@@ -3000,55 +3144,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5422
+          <t xml:space="preserve">9422
 </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>302</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1364
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
-</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1775
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
@@ -3060,18 +3210,19 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>420</t>
+          <t xml:space="preserve">490
+</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -3089,13 +3240,13 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -3107,19 +3258,19 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
+          <t xml:space="preserve">2863
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -3131,7 +3282,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2176
 </t>
         </is>
       </c>
@@ -3149,13 +3300,14 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15363
+          <t xml:space="preserve">5363
 </t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t xml:space="preserve">318
+</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -3166,19 +3318,19 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12225
+          <t xml:space="preserve">2125
 </t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -3196,23 +3348,28 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
-</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="n"/>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">510
@@ -3227,7 +3384,8 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>243</t>
+          <t xml:space="preserve">313
+</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
@@ -3238,19 +3396,19 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2390
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
@@ -3262,7 +3420,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
@@ -3274,13 +3432,13 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -3298,13 +3456,13 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2315
+          <t xml:space="preserve">25175
 </t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1603
+          <t xml:space="preserve">1605
 </t>
         </is>
       </c>
@@ -3316,19 +3474,18 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11171
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">1868
 </t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600
+          <t xml:space="preserve">1610
 </t>
         </is>
       </c>
@@ -3352,55 +3509,55 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7191
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">503
 </t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12120
+          <t xml:space="preserve">2720
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412
+          <t xml:space="preserve">412
 </t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1544
+          <t xml:space="preserve">1344
 </t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">735
 </t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
+          <t xml:space="preserve">566
 </t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1829
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
@@ -3412,7 +3569,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13026
+          <t xml:space="preserve">1388
 </t>
         </is>
       </c>
@@ -3424,7 +3581,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
@@ -3436,7 +3593,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11224
+          <t xml:space="preserve">11274
 </t>
         </is>
       </c>
@@ -3454,91 +3611,103 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3095
-</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">046
+</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">346
+</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">309
+</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">147
 </t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="n"/>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="n"/>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">046
-</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1147
-</t>
-        </is>
-      </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
@@ -3559,27 +3728,22 @@
 </t>
         </is>
       </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
+      <c r="W24" s="2" t="inlineStr"/>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="Z24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3597,42 +3761,44 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4255
+          <t xml:space="preserve">4555
 </t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">177
+</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">5248
 </t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1842
+          <t xml:space="preserve">1142
 </t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">61
+</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3649,57 +3815,66 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="n"/>
+          <t xml:space="preserve">1218
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1400
+          <t xml:space="preserve">400
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11140
+          <t xml:space="preserve">1040
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="n"/>
+          <t xml:space="preserve">11480
+</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">873
+</t>
+        </is>
+      </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1177
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3716,13 +3891,13 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14575
+          <t xml:space="preserve">14114
 </t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11121
+          <t xml:space="preserve">218218280
 </t>
         </is>
       </c>
@@ -3740,7 +3915,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304
+          <t xml:space="preserve">2304
 </t>
         </is>
       </c>
@@ -3752,31 +3927,32 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2225
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">8055
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3787,26 +3963,31 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="n"/>
+          <t xml:space="preserve">1105
+</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">8120
 </t>
         </is>
       </c>
@@ -3818,19 +3999,20 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">1293
 </t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1142
 </t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3847,27 +4029,31 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="X26" s="2" t="n"/>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2270
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3890,24 +4076,25 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">31 18
+</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">12356
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
@@ -3917,22 +4104,27 @@
 </t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1014
 </t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">1679
 </t>
         </is>
       </c>
@@ -3942,7 +4134,12 @@
 </t>
         </is>
       </c>
-      <c r="N27" s="2" t="n"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">220
@@ -3963,10 +4160,16 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="n"/>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1160
@@ -3975,31 +4178,32 @@
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1374
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="X27" s="2" t="n"/>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr"/>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10266
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">18659
 </t>
         </is>
       </c>
@@ -4017,143 +4221,144 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16210
-</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
+          <t xml:space="preserve">352
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">104646
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1816
+</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1004
+</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1420
+</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11010
+</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">321
+</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2681
+</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1277
+</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1133
+</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">186
 </t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1102
-</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14280
-</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11208
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321
-</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">434
-</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1277
-</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1133
-</t>
-        </is>
-      </c>
-      <c r="X28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="Y28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
@@ -4171,7 +4376,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6249
+          <t xml:space="preserve">6248
 </t>
         </is>
       </c>
@@ -4183,13 +4388,13 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">1221
 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
@@ -4201,25 +4406,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>497</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1008
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -4231,18 +4435,19 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1413
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -4254,7 +4459,7 @@
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3835
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
@@ -4266,7 +4471,8 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t xml:space="preserve">46
+</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -4275,10 +4481,15 @@
 </t>
         </is>
       </c>
-      <c r="U29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">421
+</t>
+        </is>
+      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277
+          <t xml:space="preserve">2757
 </t>
         </is>
       </c>
@@ -4296,13 +4507,13 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30682
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -4320,7 +4531,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27819
+          <t xml:space="preserve">21819
 </t>
         </is>
       </c>
@@ -4332,7 +4543,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7145
+          <t xml:space="preserve">7265
 </t>
         </is>
       </c>
@@ -4344,7 +4555,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
@@ -4356,19 +4567,19 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1558
+          <t xml:space="preserve">1398
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
@@ -4380,13 +4591,13 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1306
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
@@ -4404,7 +4615,7 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
+          <t xml:space="preserve">1591
 </t>
         </is>
       </c>
@@ -4414,16 +4625,21 @@
 </t>
         </is>
       </c>
-      <c r="S30" s="2" t="n"/>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">318
+</t>
+        </is>
+      </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81941
+          <t xml:space="preserve">11941
 </t>
         </is>
       </c>
@@ -4441,12 +4657,21 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="2" t="n"/>
-      <c r="Z30" s="2" t="n"/>
+          <t xml:space="preserve">11900
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4461,7 +4686,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2364
+          <t xml:space="preserve">8564
 </t>
         </is>
       </c>
@@ -4473,7 +4698,8 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>489</t>
+          <t xml:space="preserve">149
+</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4484,8 +4710,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -4506,15 +4731,30 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="2" t="n"/>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">015
+</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">164
 </t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="n"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110 1
+</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">465
@@ -4535,14 +4775,18 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="n"/>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -4554,25 +4798,25 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2293
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -4596,13 +4840,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0111
-</t>
+          <t>61444</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">338
+          <t xml:space="preserve">3008
 </t>
         </is>
       </c>
@@ -4614,24 +4857,26 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112321
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">621
+</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">942
+</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -4642,22 +4887,28 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">11260
 </t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="n"/>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">390
@@ -4666,34 +4917,49 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="n"/>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">336
+</t>
+        </is>
+      </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1141
 </t>
         </is>
       </c>
-      <c r="S32" s="2" t="n"/>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="U32" s="2" t="n"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">474
+</t>
+        </is>
+      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1283
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -4703,10 +4969,15 @@
 </t>
         </is>
       </c>
-      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">349
 </t>
         </is>
       </c>
@@ -4724,7 +4995,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4487
+          <t xml:space="preserve">6137
 </t>
         </is>
       </c>
@@ -4736,13 +5007,13 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2229
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
@@ -4772,13 +5043,13 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -4790,46 +5061,56 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1410
-</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1128
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="n"/>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1147
 </t>
         </is>
       </c>
-      <c r="S33" s="2" t="n"/>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="n"/>
+          <t xml:space="preserve">302
+</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1834
+</t>
+        </is>
+      </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12180
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">2617
 </t>
         </is>
       </c>
@@ -4841,13 +5122,13 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">14554
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">1039
 </t>
         </is>
       </c>
@@ -4865,8 +5146,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3866
-</t>
+          <t>38463</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4877,21 +5157,31 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">1056
 </t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
-</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">018
+</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4909,31 +5199,31 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11160
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129522
+          <t xml:space="preserve">422
 </t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -4945,55 +5235,55 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">1324
 </t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0250
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1127
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">0118
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1010
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">18606
 </t>
         </is>
       </c>
@@ -5011,87 +5301,97 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4339
+          <t xml:space="preserve">4399
 </t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">503
+</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1170
+</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1237
+</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1149
+</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1143
+</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">886
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">303
 </t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1170
-</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="n"/>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1133
-</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1285
-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1240
-</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">303
-</t>
-        </is>
-      </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
@@ -5103,19 +5403,19 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">2111
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -5127,19 +5427,20 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18398
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5166,60 +5467,70 @@
 </t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">112
 </t>
         </is>
       </c>
-      <c r="F36" s="2" t="n"/>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
-</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1940
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -5231,30 +5542,31 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">28221
 </t>
         </is>
       </c>
@@ -5266,19 +5578,19 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188
+          <t xml:space="preserve">14988
 </t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
@@ -5296,12 +5608,13 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>9661</t>
+          <t xml:space="preserve">22166
+</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11816
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -5313,7 +5626,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11102
+          <t xml:space="preserve">110253
 </t>
         </is>
       </c>
@@ -5325,7 +5638,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">358
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -5337,30 +5650,32 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">10180
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>364</t>
+          <t xml:space="preserve">86
+</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">017
+</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -5371,65 +5686,67 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t xml:space="preserve">5935
+</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1335
+          <t xml:space="preserve">1336
 </t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17826
+          <t xml:space="preserve">726
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1478
+          <t xml:space="preserve">478
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11410
+          <t xml:space="preserve">1516
 </t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11342
+          <t xml:space="preserve">1340
 </t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">870
+</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9498
+          <t xml:space="preserve">498
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">13150
 </t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
@@ -5447,101 +5764,115 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433
+          <t xml:space="preserve">4733
 </t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>428</t>
+          <t xml:space="preserve">138
+</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1681
+</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1192
+</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1106
+</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">169
 </t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21112
-</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14180
-</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1267
-</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1148
-</t>
-        </is>
-      </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>9401</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2269
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -5589,95 +5920,106 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3146
+          <t xml:space="preserve">9146
 </t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">11921
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">114126
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">12119
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">102101
 </t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15101
+</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1102
+</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2110
+</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8187
+</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1593
+</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">100
 </t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1132
-</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11102
-</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="n"/>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="n"/>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1224
@@ -5686,32 +6028,37 @@
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
-</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="n"/>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1248
+</t>
+        </is>
+      </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3964
+          <t xml:space="preserve">964
 </t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2266
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -5729,23 +6076,24 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6171
-</t>
+          <t>64716</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>303</t>
+          <t xml:space="preserve">917
+</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262217
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
@@ -5757,25 +6105,25 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1086
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
@@ -5793,7 +6141,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">801
 </t>
         </is>
       </c>
@@ -5817,28 +6165,34 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">87
+</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7942
-</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="n"/>
+          <t xml:space="preserve">3942
+</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1847
@@ -5847,19 +6201,19 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
+          <t xml:space="preserve">2161
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81206
+          <t xml:space="preserve">380
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12216
+          <t xml:space="preserve">2216 3
 </t>
         </is>
       </c>
@@ -5883,12 +6237,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">1622
 </t>
         </is>
       </c>
@@ -5900,7 +6254,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">116621
 </t>
         </is>
       </c>
@@ -5924,7 +6278,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
@@ -5936,11 +6290,16 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="n"/>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">490
@@ -5949,7 +6308,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
@@ -5961,7 +6320,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -5973,19 +6332,19 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2926
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1275
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -5997,21 +6356,17 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1016
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18284
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
           <t>28</t>
@@ -6032,47 +6387,49 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t xml:space="preserve">3121
+</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -6088,10 +6445,15 @@
 </t>
         </is>
       </c>
-      <c r="N42" s="2" t="n"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95
+</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9209
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
@@ -6103,30 +6465,31 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t xml:space="preserve">204
+</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -6138,28 +6501,23 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="n"/>
       <c r="AA42" t="inlineStr">
         <is>
           <t>29</t>
@@ -6174,13 +6532,13 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3540
+          <t xml:space="preserve">2540
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">3056
 </t>
         </is>
       </c>
@@ -6192,7 +6550,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2239
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -6210,18 +6568,19 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t xml:space="preserve">59
+</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6231,23 +6590,33 @@
 </t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
-</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="n"/>
+          <t xml:space="preserve">9216
+</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
@@ -6259,31 +6628,31 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -6295,13 +6664,13 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19253
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2461
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -6319,7 +6688,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2380
+          <t xml:space="preserve">2280
 </t>
         </is>
       </c>
@@ -6337,7 +6706,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">12229
 </t>
         </is>
       </c>
@@ -6347,29 +6716,40 @@
 </t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6561
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
-</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="n"/>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -6386,13 +6766,13 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -6404,19 +6784,19 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1093
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -6434,7 +6814,7 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
@@ -6446,7 +6826,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1824
+          <t xml:space="preserve">11221
 </t>
         </is>
       </c>
@@ -6462,144 +6842,140 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">331029
-</t>
-        </is>
-      </c>
+      <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118715
+          <t xml:space="preserve">15551
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1919
+          <t xml:space="preserve">4119
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11221
+          <t xml:space="preserve">11021
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822246
+          <t xml:space="preserve">3450
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15123
+          <t xml:space="preserve">2263
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18222
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110111
+          <t xml:space="preserve">12919
 </t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18159
-</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr"/>
+          <t xml:space="preserve">801
+</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112265
+          <t xml:space="preserve">1022615
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">9204
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t xml:space="preserve">1284
+</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10218
+          <t xml:space="preserve">0118
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1838
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18369
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88886
+          <t xml:space="preserve">1026
 </t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214621
+          <t xml:space="preserve">1412
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1061
+          <t xml:space="preserve">01010
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10987
+          <t xml:space="preserve">18 8
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12228
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11172
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">12224
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -6614,13 +6990,13 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518
-</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t xml:space="preserve">706
+</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -6631,25 +7007,26 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">9010
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -6658,23 +7035,28 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="2" t="n"/>
+      <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1808
+</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
@@ -6686,13 +7068,13 @@
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -6704,27 +7086,37 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3908
-</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="n"/>
-      <c r="W46" s="2" t="n"/>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">848
+</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1144
+</t>
+        </is>
+      </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/501/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/501/Midpoint_Excel_with_OCR_Results.xlsx
@@ -626,19 +626,19 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5628
+          <t xml:space="preserve">5698
 </t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">937
 </t>
         </is>
       </c>
@@ -656,7 +656,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -686,13 +686,13 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -710,13 +710,13 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -752,8 +752,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151 27 1
-</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -764,7 +763,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
@@ -776,13 +775,13 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">764
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -794,19 +793,19 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -818,7 +817,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
@@ -854,12 +853,13 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>04449</t>
+          <t xml:space="preserve">122
+</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -883,13 +883,13 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
@@ -907,7 +907,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23048
+          <t xml:space="preserve">3068
 </t>
         </is>
       </c>
@@ -925,13 +925,13 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">2231
 </t>
         </is>
       </c>
@@ -943,79 +943,79 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1008
+</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">85
 </t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">327
+</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">122
 </t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21098
-</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">327
-</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">0910
 </t>
         </is>
       </c>
@@ -1027,8 +1027,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1642
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
@@ -1039,13 +1038,13 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">302
 </t>
         </is>
       </c>
@@ -1093,13 +1092,13 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -1111,7 +1110,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -1123,13 +1122,13 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -1147,19 +1146,18 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">347
 </t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -1183,14 +1181,12 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>863</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
@@ -1201,7 +1197,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1218,7 +1214,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112851
+          <t xml:space="preserve">2851
 </t>
         </is>
       </c>
@@ -1236,7 +1232,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2828
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -1254,25 +1250,25 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0110
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1161
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -1285,7 +1281,7 @@
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
+          <t xml:space="preserve">32620
 </t>
         </is>
       </c>
@@ -1309,7 +1305,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
@@ -1327,13 +1323,13 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -1354,28 +1350,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26660
-</t>
+          <t>196565</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1697
+          <t xml:space="preserve">11697
 </t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14134
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">383
+</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1164
@@ -1384,25 +1374,25 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3291
+          <t xml:space="preserve">391
 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6142
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
+          <t xml:space="preserve">1684
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -1414,7 +1404,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
@@ -1432,7 +1422,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">487
+          <t xml:space="preserve">497
 </t>
         </is>
       </c>
@@ -1492,7 +1482,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11584
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
@@ -1510,25 +1500,25 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
+          <t xml:space="preserve">5312
 </t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1872
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -1540,8 +1530,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1578,7 +1567,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -1596,7 +1585,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -1608,7 +1597,7 @@
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">448
 </t>
         </is>
       </c>
@@ -1626,13 +1615,13 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -1662,8 +1651,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3080
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1674,25 +1662,25 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -1704,7 +1692,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -1716,11 +1704,16 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">614
-</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1130
@@ -1741,25 +1734,25 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8210
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -1788,24 +1781,19 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
-</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">10217
 </t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -1829,7 +1817,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
@@ -1865,31 +1853,30 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3108
+          <t xml:space="preserve">3118
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -1907,19 +1894,19 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">1623
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12170
+          <t xml:space="preserve">14170
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18358
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -1949,7 +1936,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1594
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -1961,20 +1948,14 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
-</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2004,7 +1985,7 @@
       <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">8490
 </t>
         </is>
       </c>
@@ -2022,7 +2003,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
@@ -2040,37 +2021,36 @@
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1021
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">088
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2099,7 +2079,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -2111,7 +2091,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -2135,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -2147,7 +2127,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -2172,49 +2152,49 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">045
+</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">738
+</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">360
+</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">270
+</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">145
 </t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">360
-</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">270
-</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0808
+          <t xml:space="preserve">10208
 </t>
         </is>
       </c>
@@ -2233,29 +2213,28 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2521
+          <t xml:space="preserve">26521
 </t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>731</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
@@ -2291,7 +2270,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -2303,7 +2282,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1488
 </t>
         </is>
       </c>
@@ -2315,48 +2294,42 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3120
-</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1145
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">310
+</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr"/>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">2008
 </t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38208
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>981</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -2376,25 +2349,25 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2371
+          <t xml:space="preserve">2572
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1823916
+          <t xml:space="preserve">82916
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2168
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">11182
 </t>
         </is>
       </c>
@@ -2424,31 +2397,26 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1898
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22120
+          <t xml:space="preserve">22125
 </t>
         </is>
       </c>
@@ -2460,7 +2428,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1547
+          <t xml:space="preserve">1847
 </t>
         </is>
       </c>
@@ -2478,25 +2446,25 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1315
+          <t xml:space="preserve">1313
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -2508,7 +2476,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11438
+          <t xml:space="preserve">1458
 </t>
         </is>
       </c>
@@ -2532,31 +2500,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3154
+          <t xml:space="preserve">23134
 </t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3819
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22316
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -2578,16 +2545,21 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">2104
 </t>
         </is>
       </c>
@@ -2599,7 +2571,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
@@ -2623,7 +2595,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
@@ -2635,7 +2607,7 @@
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9816
+          <t xml:space="preserve">9274
 </t>
         </is>
       </c>
@@ -2664,7 +2636,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -2682,7 +2654,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10321
+          <t xml:space="preserve">2321
 </t>
         </is>
       </c>
@@ -2694,7 +2666,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2703,26 +2675,21 @@
 </t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
+      <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2745,7 +2712,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -2763,13 +2730,13 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2804
+          <t xml:space="preserve">2806
 </t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -2781,7 +2748,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
@@ -2793,7 +2760,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1081
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
@@ -2805,19 +2772,19 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">2928
 </t>
         </is>
       </c>
@@ -2835,18 +2802,19 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">354
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2867,15 +2835,10 @@
 </t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11206
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -2887,8 +2850,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2899,7 +2861,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
@@ -2929,7 +2891,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
@@ -2941,14 +2903,13 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1614
+          <t xml:space="preserve">414
 </t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>969</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2959,13 +2920,13 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -2989,26 +2950,23 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93905
-</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3019,7 +2977,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9149
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -3031,7 +2989,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3042,7 +3000,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
@@ -3054,13 +3012,13 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">550
 </t>
         </is>
       </c>
@@ -3090,8 +3048,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>448</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -3102,25 +3059,25 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16202
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
@@ -3144,25 +3101,25 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422
+          <t xml:space="preserve">0422
 </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">1864
 </t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -3180,7 +3137,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
@@ -3192,13 +3149,13 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">1757
 </t>
         </is>
       </c>
@@ -3264,7 +3221,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -3276,13 +3233,13 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2176
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -3300,7 +3257,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5363
+          <t xml:space="preserve">9363
 </t>
         </is>
       </c>
@@ -3318,7 +3275,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -3366,7 +3323,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -3402,13 +3359,13 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">1849
 </t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">2390
 </t>
         </is>
       </c>
@@ -3420,13 +3377,13 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
@@ -3462,30 +3419,31 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
+          <t xml:space="preserve">1603
 </t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
+          <t xml:space="preserve">735
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t xml:space="preserve">11171
+</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1868
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1610
+          <t xml:space="preserve">1600
 </t>
         </is>
       </c>
@@ -3509,7 +3467,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -3521,37 +3479,37 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2720
+          <t xml:space="preserve">12720
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">412
+          <t xml:space="preserve">413
 </t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1344
+          <t xml:space="preserve">2544
 </t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">735
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">566
+          <t xml:space="preserve">3686
 </t>
         </is>
       </c>
@@ -3569,13 +3527,13 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1388
+          <t xml:space="preserve">1386
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1688
+          <t xml:space="preserve">688
 </t>
         </is>
       </c>
@@ -3593,7 +3551,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11274
+          <t xml:space="preserve">11224
 </t>
         </is>
       </c>
@@ -3611,12 +3569,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
@@ -3628,7 +3586,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">2234
 </t>
         </is>
       </c>
@@ -3640,7 +3598,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">1022
 </t>
         </is>
       </c>
@@ -3652,16 +3610,11 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1174
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -3670,19 +3623,19 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">046
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">346
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -3694,7 +3647,7 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -3712,7 +3665,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -3728,7 +3681,11 @@
 </t>
         </is>
       </c>
-      <c r="W24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">86
@@ -3737,13 +3694,13 @@
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3779,7 +3736,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5248
+          <t xml:space="preserve">10248
 </t>
         </is>
       </c>
@@ -3821,42 +3778,43 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">400
+          <t xml:space="preserve">4010
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11480
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">873
+          <t xml:space="preserve">8373
 </t>
         </is>
       </c>
@@ -3868,18 +3826,18 @@
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>37</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -3891,13 +3849,12 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14114
-</t>
+          <t>416</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218218280
+          <t xml:space="preserve">11121
 </t>
         </is>
       </c>
@@ -3915,7 +3872,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2304
+          <t xml:space="preserve">5304
 </t>
         </is>
       </c>
@@ -3939,7 +3896,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8055
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
@@ -3987,7 +3944,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8120
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -3999,13 +3956,12 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1293
-</t>
+          <t>993</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -4017,7 +3973,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
@@ -4029,13 +3985,13 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -4047,13 +4003,13 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">0220
 </t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4070,13 +4026,13 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5501
+          <t xml:space="preserve">501
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31 18
+          <t xml:space="preserve">318 4
 </t>
         </is>
       </c>
@@ -4088,13 +4044,13 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12356
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -4112,7 +4068,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1014
+          <t xml:space="preserve">1104
 </t>
         </is>
       </c>
@@ -4124,7 +4080,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1679
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -4136,19 +4092,19 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
@@ -4172,23 +4128,27 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">3174
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr"/>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
@@ -4197,13 +4157,12 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18659
+          <t xml:space="preserve">1965
 </t>
         </is>
       </c>
@@ -4221,36 +4180,37 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t xml:space="preserve">16210
+</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">352
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104646
+          <t xml:space="preserve">1376
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1816
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">1104
 </t>
         </is>
       </c>
@@ -4292,20 +4252,19 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1420
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11010
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
@@ -4316,19 +4275,19 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2681
+          <t xml:space="preserve">434
 </t>
         </is>
       </c>
@@ -4340,7 +4299,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -4356,12 +4315,7 @@
 </t>
         </is>
       </c>
-      <c r="Z28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">908
-</t>
-        </is>
-      </c>
+      <c r="Z28" s="2" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
           <t>19</t>
@@ -4388,13 +4342,13 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
@@ -4412,18 +4366,18 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>493</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">81811
 </t>
         </is>
       </c>
@@ -4447,19 +4401,19 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">413
 </t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">835
 </t>
         </is>
       </c>
@@ -4483,13 +4437,13 @@
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">421
+          <t xml:space="preserve">471
 </t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2757
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -4501,19 +4455,19 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">230090
 </t>
         </is>
       </c>
@@ -4531,19 +4485,19 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21819
+          <t xml:space="preserve">22819
 </t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1616
+          <t xml:space="preserve">15616
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7265
+          <t xml:space="preserve">7145
 </t>
         </is>
       </c>
@@ -4555,13 +4509,13 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1570
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -4573,7 +4527,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1398
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -4609,20 +4563,19 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
+          <t xml:space="preserve">917
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1591
+          <t xml:space="preserve">1551
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">709
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -4633,13 +4586,13 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11941
+          <t xml:space="preserve">1941
 </t>
         </is>
       </c>
@@ -4657,19 +4610,19 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11900
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">1069
 </t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4686,7 +4639,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8564
+          <t xml:space="preserve">2364
 </t>
         </is>
       </c>
@@ -4710,7 +4663,8 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -4727,13 +4681,13 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">015
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -4781,7 +4735,8 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">69
+</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
@@ -4840,13 +4795,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>611</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3008
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4863,19 +4817,19 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">621
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -4887,19 +4841,19 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11260
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -4917,7 +4871,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -4929,7 +4883,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -4953,7 +4907,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">1283
 </t>
         </is>
       </c>
@@ -4965,7 +4919,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -4977,7 +4931,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">349
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -4995,7 +4949,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6137
+          <t xml:space="preserve">1225
 </t>
         </is>
       </c>
@@ -5007,7 +4961,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -5019,7 +4973,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -5031,7 +4985,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -5043,7 +4997,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -5067,11 +5021,16 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr"/>
+          <t xml:space="preserve">410
+</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">260
@@ -5080,7 +5039,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -5092,25 +5051,25 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
+          <t xml:space="preserve">1934
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2617
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -5122,14 +5081,13 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14554
+          <t xml:space="preserve">1492
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1039
-</t>
+          <t>432</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5146,7 +5104,8 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>38463</t>
+          <t xml:space="preserve">3866
+</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -5169,121 +5128,121 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1814
+</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">018
 </t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1172
-</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422
-</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1324
-</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1890
-</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="X34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0118
-</t>
-        </is>
-      </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18606
+          <t xml:space="preserve">180 16
 </t>
         </is>
       </c>
@@ -5313,13 +5272,13 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -5331,7 +5290,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -5343,13 +5302,13 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -5367,7 +5326,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -5379,19 +5338,14 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
-</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">303
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">986
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -5409,7 +5363,7 @@
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2111
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
@@ -5433,16 +5387,11 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="Z35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">21215
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
           <t>24</t>
@@ -5476,34 +5425,23 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">178
@@ -5518,13 +5456,13 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -5554,7 +5492,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -5566,7 +5504,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28221
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -5584,13 +5522,13 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14988
+          <t xml:space="preserve">11860
 </t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
@@ -5614,7 +5552,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">118106
 </t>
         </is>
       </c>
@@ -5626,7 +5564,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110253
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
@@ -5638,7 +5576,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">338
 </t>
         </is>
       </c>
@@ -5650,31 +5588,31 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10180
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">032
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
@@ -5686,31 +5624,31 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5935
+          <t xml:space="preserve">893
 </t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1336
+          <t xml:space="preserve">133 5
 </t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">478
+          <t xml:space="preserve">1478
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1516
+          <t xml:space="preserve">11510
 </t>
         </is>
       </c>
@@ -5722,13 +5660,13 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">670
 </t>
         </is>
       </c>
@@ -5740,13 +5678,13 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13150
+          <t xml:space="preserve">11812
 </t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
@@ -5764,13 +5702,13 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4733
+          <t xml:space="preserve">4422
 </t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">2303
 </t>
         </is>
       </c>
@@ -5788,13 +5726,13 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1681
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -5812,7 +5750,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
@@ -5824,31 +5762,31 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
@@ -5860,7 +5798,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -5872,7 +5810,7 @@
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -5926,25 +5864,24 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11921
-</t>
+          <t>794</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114126
+          <t xml:space="preserve">1416
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12119
+          <t xml:space="preserve">11866
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102101
+          <t xml:space="preserve">108110
 </t>
         </is>
       </c>
@@ -5956,13 +5893,13 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -5974,25 +5911,24 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15101
+          <t xml:space="preserve">1151
 </t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2110
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -6004,13 +5940,13 @@
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8187
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1593
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -6022,19 +5958,19 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">0294
 </t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -6046,13 +5982,13 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">964
+          <t xml:space="preserve">364
 </t>
         </is>
       </c>
@@ -6076,12 +6012,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>64716</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
+          <t xml:space="preserve">907
 </t>
         </is>
       </c>
@@ -6093,7 +6029,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -6105,13 +6041,13 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -6123,7 +6059,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -6141,7 +6077,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -6165,7 +6101,7 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
@@ -6183,7 +6119,7 @@
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3942
+          <t xml:space="preserve">842
 </t>
         </is>
       </c>
@@ -6195,26 +6131,25 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1847
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216 3
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6237,12 +6172,13 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t xml:space="preserve">314
+</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1622
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -6254,19 +6190,19 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116621
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -6278,7 +6214,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6302,13 +6238,13 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
@@ -6332,13 +6268,13 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
@@ -6350,7 +6286,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -6360,13 +6296,12 @@
 </t>
         </is>
       </c>
-      <c r="Y41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18284
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>28</t>
@@ -6387,37 +6322,37 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3121
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -6435,7 +6370,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
@@ -6447,13 +6382,13 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -6465,7 +6400,7 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
@@ -6477,13 +6412,13 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -6501,19 +6436,19 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6532,13 +6467,13 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2540
+          <t xml:space="preserve">5340
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3056
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
@@ -6562,7 +6497,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">1834
 </t>
         </is>
       </c>
@@ -6592,19 +6527,19 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9216
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -6622,7 +6557,7 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -6640,7 +6575,7 @@
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -6652,7 +6587,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -6670,7 +6605,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
@@ -6700,13 +6635,13 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12229
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -6736,7 +6671,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -6748,19 +6683,18 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1440
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -6778,25 +6712,25 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
+          <t xml:space="preserve">1123
 </t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">3228
 </t>
         </is>
       </c>
@@ -6808,28 +6742,22 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="Z44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11221
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">508
+</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
           <t>31</t>
@@ -6842,58 +6770,63 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18011
+</t>
+        </is>
+      </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15551
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4119
+          <t xml:space="preserve">917
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11021
+          <t xml:space="preserve">11221
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450
+          <t xml:space="preserve">7211
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2263
+          <t xml:space="preserve">523
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12919
+          <t xml:space="preserve">12818
 </t>
         </is>
       </c>
@@ -6905,73 +6838,68 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022615
+          <t xml:space="preserve">12265
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9204
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
+          <t xml:space="preserve">1700
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0118
+          <t xml:space="preserve">0815
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
-</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1026
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1264
+</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412
+          <t xml:space="preserve">1442
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01010
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 8
+          <t xml:space="preserve">1 1
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12224
+          <t xml:space="preserve">12229
 </t>
         </is>
       </c>
@@ -6990,30 +6918,30 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">706
+          <t xml:space="preserve">406
 </t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9010
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -7025,7 +6953,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -7035,7 +6963,12 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">168
@@ -7056,7 +6989,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">494
 </t>
         </is>
       </c>
@@ -7074,7 +7007,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -7092,19 +7025,19 @@
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
@@ -7116,13 +7049,13 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">1126
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/501/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/501/Midpoint_Excel_with_OCR_Results.xlsx
@@ -4985,7 +4985,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/501/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/501/Midpoint_Excel_with_OCR_Results.xlsx
@@ -4985,7 +4985,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/501/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/501/Midpoint_Excel_with_OCR_Results.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">937
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -656,7 +656,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -674,7 +674,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -692,13 +692,13 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">345
+          <t xml:space="preserve">355
 </t>
         </is>
       </c>
@@ -710,19 +710,19 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -752,7 +752,8 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t xml:space="preserve">5127
+</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -763,19 +764,19 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
@@ -799,7 +800,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">008
 </t>
         </is>
       </c>
@@ -811,19 +812,14 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
+          <t xml:space="preserve">1360
 </t>
         </is>
       </c>
@@ -841,7 +837,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1840
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -853,37 +849,37 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1468
+</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">968
 </t>
         </is>
       </c>
@@ -907,7 +903,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3068
+          <t xml:space="preserve">5048
 </t>
         </is>
       </c>
@@ -931,7 +927,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2231
+          <t xml:space="preserve">20239
 </t>
         </is>
       </c>
@@ -943,7 +939,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -955,13 +951,13 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -971,21 +967,16 @@
 </t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+      <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1008
+          <t xml:space="preserve">1400
 </t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -997,13 +988,13 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1152
 </t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -1015,7 +1006,7 @@
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0910
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
@@ -1027,7 +1018,8 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">142
+</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
@@ -1044,7 +1036,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">2302
 </t>
         </is>
       </c>
@@ -1068,13 +1060,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">353
-</t>
+          <t>353</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -1086,13 +1077,13 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -1110,7 +1101,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -1122,13 +1113,13 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -1152,12 +1143,13 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t xml:space="preserve">1138
+</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -1181,23 +1173,26 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">135
+</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">334
+</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1214,13 +1209,13 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2851
+          <t xml:space="preserve">4851
 </t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">344
 </t>
         </is>
       </c>
@@ -1244,44 +1239,44 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32620
+          <t xml:space="preserve">362
 </t>
         </is>
       </c>
@@ -1311,31 +1306,45 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">291
+</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1133
+</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">143
 </t>
         </is>
       </c>
-      <c r="U8" s="2" t="inlineStr">
+      <c r="Y8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">422
 </t>
         </is>
       </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="X8" s="2" t="n"/>
-      <c r="Y8" s="2" t="n"/>
-      <c r="Z8" s="2" t="n"/>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>5</t>
@@ -1350,22 +1359,28 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>196565</t>
+          <t xml:space="preserve">26361
+</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11697
+          <t xml:space="preserve">1697
 </t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">383
-</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1233
+</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11134
+</t>
+        </is>
+      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1164
@@ -1380,25 +1395,25 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">442
 </t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1684
+          <t xml:space="preserve">684
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">671
+          <t xml:space="preserve">1671
 </t>
         </is>
       </c>
@@ -1410,37 +1425,37 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1830
+          <t xml:space="preserve">11830
 </t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">497
+          <t xml:space="preserve">487
 </t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">1650
 </t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">1718
 </t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">1277
 </t>
         </is>
       </c>
@@ -1452,7 +1467,7 @@
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12241
+          <t xml:space="preserve">2248
 </t>
         </is>
       </c>
@@ -1476,7 +1491,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11862
+          <t xml:space="preserve">1367
 </t>
         </is>
       </c>
@@ -1512,25 +1527,26 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">1232
 </t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">1478
+</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1545,7 +1561,7 @@
 </t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">134
@@ -1558,7 +1574,7 @@
 </t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">366
@@ -1567,7 +1583,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -1609,25 +1625,25 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">389
 </t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">11062
+</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -1651,7 +1667,8 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>305</t>
+          <t xml:space="preserve">308
+</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1662,7 +1679,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
@@ -1680,19 +1697,19 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1469
 </t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -1716,7 +1733,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -1734,7 +1751,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -1746,13 +1763,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">1310
 </t>
         </is>
       </c>
@@ -1781,19 +1797,19 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10217
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
@@ -1817,7 +1833,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1835,7 +1851,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -1847,36 +1863,36 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3118
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">142
+</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -1888,25 +1904,25 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1840
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1623
+          <t xml:space="preserve">1023
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14170
+          <t xml:space="preserve">470
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -1936,8 +1952,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>424</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1952,10 +1967,16 @@
 </t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1114
+</t>
+        </is>
+      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t xml:space="preserve">94
+</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1982,10 +2003,10 @@
 </t>
         </is>
       </c>
-      <c r="N13" s="2" t="n"/>
+      <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8490
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
@@ -2003,7 +2024,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
@@ -2021,7 +2042,7 @@
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
@@ -2045,12 +2066,14 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">288
+</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t xml:space="preserve">254
+</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2067,7 +2090,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
+          <t xml:space="preserve">4880
 </t>
         </is>
       </c>
@@ -2079,7 +2102,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -2115,7 +2138,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2127,14 +2150,14 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">495
 </t>
         </is>
       </c>
@@ -2146,19 +2169,19 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">2303
 </t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">045
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">738
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
@@ -2170,35 +2193,40 @@
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
+          <t xml:space="preserve">4490
 </t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">270
 </t>
         </is>
       </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="X14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="Y14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10208
-</t>
-        </is>
-      </c>
-      <c r="Z14" s="2" t="n"/>
       <c r="AA14" t="inlineStr">
         <is>
           <t>9</t>
@@ -2213,23 +2241,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26521
+          <t xml:space="preserve">5529
 </t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>313</t>
+          <t xml:space="preserve">315
+</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">150
+</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t xml:space="preserve">1231
+</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2270,19 +2301,14 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1104
+</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1488
+          <t xml:space="preserve">4180
 </t>
         </is>
       </c>
@@ -2294,47 +2320,64 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2310
+</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1145
+</t>
+        </is>
+      </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">1154
 </t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">380
+</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t xml:space="preserve">271
+</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">84
 </t>
         </is>
       </c>
-      <c r="Y15" s="2" t="n"/>
-      <c r="Z15" s="2" t="n"/>
       <c r="AA15" t="inlineStr">
         <is>
           <t>10</t>
@@ -2349,25 +2392,25 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2572
+          <t xml:space="preserve">2377
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82916
+          <t xml:space="preserve">129 16
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">768
 </t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11182
+          <t xml:space="preserve">21182
 </t>
         </is>
       </c>
@@ -2379,19 +2422,19 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">973
+          <t xml:space="preserve">3973
 </t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">562
+          <t xml:space="preserve">1362
 </t>
         </is>
       </c>
@@ -2401,22 +2444,27 @@
 </t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8809
+</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">521
 </t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22125
+          <t xml:space="preserve">2125
 </t>
         </is>
       </c>
@@ -2428,13 +2476,13 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1847
+          <t xml:space="preserve">1547
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">1736
 </t>
         </is>
       </c>
@@ -2446,13 +2494,13 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">1882
 </t>
         </is>
       </c>
@@ -2464,7 +2512,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2476,13 +2524,13 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1458
+          <t xml:space="preserve">11458
 </t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10244
+          <t xml:space="preserve">12244
 </t>
         </is>
       </c>
@@ -2500,19 +2548,20 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23134
+          <t xml:space="preserve">3154
 </t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>244</t>
+          <t xml:space="preserve">134
+</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2523,7 +2572,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
@@ -2535,7 +2584,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -2547,7 +2596,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -2559,19 +2608,19 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2104
+          <t xml:space="preserve">1104
 </t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">425
 </t>
         </is>
       </c>
@@ -2601,24 +2650,25 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9274
+          <t xml:space="preserve">376
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9465</t>
+          <t xml:space="preserve">263
+</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
@@ -2636,7 +2686,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -2654,44 +2704,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2321
+          <t xml:space="preserve">2521
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0229
+          <t xml:space="preserve">529
 </t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1124
+</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
-</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -2700,25 +2753,25 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">1375
 </t>
         </is>
       </c>
@@ -2730,7 +2783,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2806
+          <t xml:space="preserve">8291
 </t>
         </is>
       </c>
@@ -2748,31 +2801,31 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">1155
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">404
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">1844
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -2784,7 +2837,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2928
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -2802,7 +2855,8 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t xml:space="preserve">3264
+</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2835,10 +2889,15 @@
 </t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1206
 </t>
         </is>
       </c>
@@ -2850,7 +2909,8 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t xml:space="preserve">135
+</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2867,7 +2927,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
+          <t xml:space="preserve">1605
 </t>
         </is>
       </c>
@@ -2885,7 +2945,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -2909,7 +2969,8 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t xml:space="preserve">1269
+</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2920,7 +2981,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
@@ -2950,23 +3011,24 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>343</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2989,12 +3051,13 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">84
+</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -3012,7 +3075,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -3048,7 +3111,8 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t xml:space="preserve">225
+</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -3059,13 +3123,13 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
@@ -3113,13 +3177,13 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1864
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -3131,7 +3195,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -3149,19 +3213,19 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1757
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -3173,7 +3237,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
@@ -3203,7 +3267,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
@@ -3215,13 +3279,13 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2863
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -3239,8 +3303,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>446</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3257,7 +3320,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9363
+          <t xml:space="preserve">5363
 </t>
         </is>
       </c>
@@ -3299,13 +3362,13 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">020
 </t>
         </is>
       </c>
@@ -3317,22 +3380,17 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">510
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9
+</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">92
@@ -3359,7 +3417,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
@@ -3371,20 +3429,19 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3425,13 +3482,13 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">735
+          <t xml:space="preserve">725
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11171
+          <t xml:space="preserve">1171
 </t>
         </is>
       </c>
@@ -3467,7 +3524,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">791
 </t>
         </is>
       </c>
@@ -3479,37 +3536,32 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12720
+          <t xml:space="preserve">2720
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
+          <t xml:space="preserve">412
 </t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2544
-</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1544
+</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3686
+          <t xml:space="preserve">366
 </t>
         </is>
       </c>
@@ -3527,19 +3579,19 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1386
+          <t xml:space="preserve">1305
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
+          <t xml:space="preserve">1688
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">1428
 </t>
         </is>
       </c>
@@ -3551,7 +3603,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11224
+          <t xml:space="preserve">1274
 </t>
         </is>
       </c>
@@ -3569,7 +3621,8 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t xml:space="preserve">5095
+</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3580,62 +3633,62 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1
 </t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2234
-</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1022
-</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1174
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2946
 </t>
         </is>
       </c>
@@ -3647,7 +3700,7 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
@@ -3683,7 +3736,8 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">138
+</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
@@ -3700,7 +3754,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -3718,7 +3772,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4555
+          <t xml:space="preserve">455
 </t>
         </is>
       </c>
@@ -3730,114 +3784,115 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1248
+</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1142
+</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61
+</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">400
+</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1262
+</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1328
+</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">177
 </t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10248
-</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1142
-</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1109
-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1118
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4010
-</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1140
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1148
-</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8373
-</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1222
-</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
@@ -3849,12 +3904,13 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t xml:space="preserve">4573
+</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11121
+          <t xml:space="preserve">2212
 </t>
         </is>
       </c>
@@ -3884,25 +3940,25 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -3926,13 +3982,13 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -3956,7 +4012,8 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t xml:space="preserve">293
+</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
@@ -3979,13 +4036,13 @@
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
+          <t xml:space="preserve">1334
 </t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
@@ -3997,19 +4054,20 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0220
+          <t xml:space="preserve">2220
 </t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">250
+</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4026,13 +4084,13 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">501
+          <t xml:space="preserve">5501
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318 4
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
@@ -4062,13 +4120,13 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -4092,19 +4150,19 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -4116,53 +4174,55 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3174
+          <t xml:space="preserve">374
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">148
+</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t xml:space="preserve">1266
+</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1965
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
@@ -4180,7 +4240,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16210
+          <t xml:space="preserve">6210
 </t>
         </is>
       </c>
@@ -4192,25 +4252,25 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1376
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -4222,13 +4282,13 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4246,13 +4306,13 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
@@ -4264,7 +4324,8 @@
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t xml:space="preserve">321
+</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
@@ -4275,25 +4336,25 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">5984
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">434
+          <t xml:space="preserve">934
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -4305,7 +4366,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -4315,7 +4376,11 @@
 </t>
         </is>
       </c>
-      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>19</t>
@@ -4330,7 +4395,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6248
+          <t xml:space="preserve">6249
 </t>
         </is>
       </c>
@@ -4348,7 +4413,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">2383
 </t>
         </is>
       </c>
@@ -4372,12 +4437,13 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>493</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81811
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4413,7 +4479,7 @@
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
@@ -4437,7 +4503,7 @@
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">471
+          <t xml:space="preserve">1471
 </t>
         </is>
       </c>
@@ -4449,8 +4515,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
@@ -4467,7 +4532,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230090
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
@@ -4485,19 +4550,19 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22819
+          <t xml:space="preserve">27819
 </t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15616
+          <t xml:space="preserve">1616
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7145
+          <t xml:space="preserve">745
 </t>
         </is>
       </c>
@@ -4515,25 +4580,25 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">570
 </t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">2370
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1358
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -4557,7 +4622,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2223
+          <t xml:space="preserve">2323
 </t>
         </is>
       </c>
@@ -4569,24 +4634,25 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1551
+          <t xml:space="preserve">1531
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -4604,25 +4670,20 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1668
-</t>
-        </is>
-      </c>
-      <c r="X30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1100
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">668
+</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr"/>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1069
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">1229
+</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4639,7 +4700,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2364
+          <t xml:space="preserve">3364
 </t>
         </is>
       </c>
@@ -4681,16 +4742,11 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1112
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">164
@@ -4699,16 +4755,11 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110 1
-</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1101
+</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">465
@@ -4717,7 +4768,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
@@ -4735,7 +4786,7 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4771,16 +4822,11 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="Z31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1273
+</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -4795,12 +4841,14 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t xml:space="preserve">2086
+</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>238</t>
+          <t xml:space="preserve">338
+</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4821,12 +4869,7 @@
 </t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
+      <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">92
@@ -4841,13 +4884,13 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
@@ -4859,7 +4902,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -4871,7 +4914,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -4895,19 +4938,18 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">474
-</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1283
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
@@ -4917,22 +4959,15 @@
 </t>
         </is>
       </c>
-      <c r="X32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
+      <c r="X32" s="2" t="inlineStr"/>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>341</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4949,7 +4984,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1225
+          <t xml:space="preserve">4437
 </t>
         </is>
       </c>
@@ -4961,7 +4996,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">1143
 </t>
         </is>
       </c>
@@ -4973,7 +5008,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">1167
 </t>
         </is>
       </c>
@@ -4985,7 +5020,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -5003,19 +5038,19 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -5039,7 +5074,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1147
 </t>
         </is>
       </c>
@@ -5057,7 +5092,7 @@
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1934
+          <t xml:space="preserve">1834
 </t>
         </is>
       </c>
@@ -5069,7 +5104,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -5081,13 +5116,14 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1492
+          <t xml:space="preserve">14209
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">1139
+</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5116,8 +5152,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1056
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -5128,19 +5163,19 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1152
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5164,13 +5199,13 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5194,19 +5229,19 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -5218,31 +5253,31 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180 16
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -5260,13 +5295,13 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4399
+          <t xml:space="preserve">4339
 </t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
@@ -5284,13 +5319,13 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1133
 </t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
@@ -5302,14 +5337,13 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>471</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -5326,7 +5360,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5342,16 +5376,21 @@
 </t>
         </is>
       </c>
-      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">308
+</t>
+        </is>
+      </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1589
 </t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -5363,7 +5402,7 @@
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
@@ -5387,11 +5426,16 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21215
-</t>
-        </is>
-      </c>
-      <c r="Z35" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>24</t>
@@ -5412,35 +5456,45 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">1048
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
@@ -5462,7 +5516,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
@@ -5486,19 +5540,19 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -5510,25 +5564,25 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1806
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11860
+          <t xml:space="preserve">1466
 </t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
@@ -5552,7 +5606,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118106
+          <t xml:space="preserve">1316
 </t>
         </is>
       </c>
@@ -5564,7 +5618,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
@@ -5576,7 +5630,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">338
+          <t xml:space="preserve">558
 </t>
         </is>
       </c>
@@ -5588,13 +5642,13 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">361
 </t>
         </is>
       </c>
@@ -5606,31 +5660,31 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">032
+          <t xml:space="preserve">1532
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">447
 </t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12402
+          <t xml:space="preserve">24092
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">893
+          <t xml:space="preserve">3595
 </t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133 5
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -5648,7 +5702,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11510
+          <t xml:space="preserve">1716
 </t>
         </is>
       </c>
@@ -5660,31 +5714,26 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">11411
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
-</t>
-        </is>
-      </c>
-      <c r="X37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">498
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr"/>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11812
+          <t xml:space="preserve">1882
 </t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
@@ -5702,19 +5751,19 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4422
+          <t xml:space="preserve">4433
 </t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2303
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
@@ -5726,13 +5775,13 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -5744,19 +5793,14 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
@@ -5768,37 +5812,37 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -5810,13 +5854,13 @@
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">1269
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
@@ -5858,30 +5902,31 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9146
+          <t xml:space="preserve">59146
 </t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t xml:space="preserve">292
+</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11866
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108110
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -5893,37 +5938,38 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
+          <t xml:space="preserve">11580
 </t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">9
+</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -5958,13 +6004,13 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0294
+          <t xml:space="preserve">1294
 </t>
         </is>
       </c>
@@ -5982,7 +6028,7 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -5994,7 +6040,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -6012,12 +6058,13 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>6414</t>
+          <t xml:space="preserve">6171
+</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">907
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
@@ -6047,7 +6094,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -6059,13 +6106,13 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -6077,13 +6124,13 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
@@ -6101,13 +6148,13 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -6119,13 +6166,13 @@
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">842
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">12680
 </t>
         </is>
       </c>
@@ -6137,19 +6184,20 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">3180
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">2236
+</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6178,25 +6226,24 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1152
 </t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1530
 </t>
         </is>
       </c>
@@ -6226,19 +6273,19 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
@@ -6268,13 +6315,13 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">2326
 </t>
         </is>
       </c>
@@ -6286,20 +6333,26 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1016
-</t>
-        </is>
-      </c>
-      <c r="Y41" s="2" t="inlineStr"/>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1289
+</t>
+        </is>
+      </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">264
+</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6322,7 +6375,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">392
 </t>
         </is>
       </c>
@@ -6334,13 +6387,13 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">1233
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
@@ -6358,7 +6411,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -6376,26 +6429,25 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -6418,7 +6470,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">1287
 </t>
         </is>
       </c>
@@ -6430,13 +6482,13 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -6448,11 +6500,16 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="2" t="n"/>
+          <t xml:space="preserve">13920
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>29</t>
@@ -6467,13 +6524,13 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340
+          <t xml:space="preserve">2340
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
@@ -6491,13 +6548,13 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
@@ -6515,7 +6572,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -6533,7 +6590,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -6545,7 +6602,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -6569,13 +6626,13 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">2314
 </t>
         </is>
       </c>
@@ -6587,7 +6644,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -6605,7 +6662,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -6623,7 +6680,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2280
+          <t xml:space="preserve">2580
 </t>
         </is>
       </c>
@@ -6641,7 +6698,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
@@ -6671,7 +6728,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">092
 </t>
         </is>
       </c>
@@ -6683,24 +6740,25 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">6440
 </t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
@@ -6712,7 +6770,7 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -6724,13 +6782,13 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3228
+          <t xml:space="preserve">2328
 </t>
         </is>
       </c>
@@ -6748,16 +6806,22 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">12279
+</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">508
-</t>
-        </is>
-      </c>
-      <c r="Z44" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2908
+</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1124
+</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>31</t>
@@ -6772,43 +6836,42 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18011
+          <t xml:space="preserve">23122
 </t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1851
+          <t xml:space="preserve">1887
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11221
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">9108
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">71949
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7211
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
@@ -6820,89 +6883,84 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12818
+          <t xml:space="preserve">1019
 </t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">12029
 </t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12265
+          <t xml:space="preserve">2265
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">29084
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1700
-</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0815
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1780
+</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
-</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1369
+</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1826
+</t>
+        </is>
+      </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1442
+          <t xml:space="preserve">1462
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">2862
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 1
-</t>
-        </is>
-      </c>
-      <c r="Y45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12229
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1647
+</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr"/>
       <c r="Z45" s="2" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
@@ -6918,30 +6976,31 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t xml:space="preserve">5518
+</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">406
+          <t xml:space="preserve">4706
 </t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -6953,7 +7012,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -6963,12 +7022,7 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">168
@@ -6977,19 +7031,19 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">494
+          <t xml:space="preserve">1494
 </t>
         </is>
       </c>
@@ -7007,13 +7061,13 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">1390
 </t>
         </is>
       </c>
@@ -7025,13 +7079,13 @@
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">23908
 </t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">2848
 </t>
         </is>
       </c>
@@ -7043,19 +7097,19 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/501/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/501/Midpoint_Excel_with_OCR_Results.xlsx
@@ -626,110 +626,92 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5698
-</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
-</t>
+          <t>335</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">355
-</t>
+          <t>355</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="U4" s="2" t="n"/>
@@ -752,141 +734,118 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1360
-</t>
+          <t>360</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
-</t>
+          <t>317</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1468
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
-</t>
+          <t>322</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -903,141 +862,118 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5048
-</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">339
-</t>
+          <t>339</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20239
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1400
-</t>
+          <t>400</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
-</t>
+          <t>327</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
-</t>
+          <t>410</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2302
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1054,8 +990,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5836
-</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1065,134 +1000,112 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">350
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">347
-</t>
+          <t>347</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">424
-</t>
+          <t>424</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1209,135 +1122,113 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4851
-</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">362
-</t>
+          <t>362</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>517</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">422
-</t>
+          <t>422</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1359,146 +1250,122 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26361
-</t>
+          <t>26560</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1697
-</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
-</t>
+          <t>533</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11134
-</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
-</t>
+          <t>391</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
-</t>
+          <t>442</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
-</t>
+          <t>684</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1671
-</t>
+          <t>671</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11830
-</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">487
-</t>
+          <t>497</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650
-</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
-</t>
+          <t>718</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2248
-</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
-</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1696
-</t>
+          <t>696</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1367
-</t>
+          <t>367</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1515,136 +1382,114 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312
-</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>339</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1478
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
-</t>
+          <t>366</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">448
-</t>
+          <t>448</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">389
-</t>
+          <t>389</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11062
-</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,104 +1506,87 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1768,8 +1596,7 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="V11" s="2" t="n"/>
@@ -1791,8 +1618,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2067
-</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1803,74 +1629,62 @@
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
-</t>
+          <t>530</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
@@ -1880,50 +1694,42 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1023
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1940,14 +1746,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6013
-</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">343
-</t>
+          <t>343</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1957,123 +1761,103 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
-</t>
+          <t>490</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
-</t>
+          <t>392</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2090,141 +1874,118 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4880
-</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
-</t>
+          <t>495</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4490
-</t>
+          <t>440</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2241,141 +2002,118 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5529
-</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180
-</t>
+          <t>480</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
-</t>
+          <t>380</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2392,146 +2130,122 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2377
-</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129 16
-</t>
+          <t>159 6</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
-</t>
+          <t>768</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21182
-</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
-</t>
+          <t>828</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
-</t>
+          <t>618</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3973
-</t>
+          <t>353</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1362
-</t>
+          <t>562</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8809
-</t>
+          <t>899</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125
-</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
-</t>
+          <t>622</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1547
-</t>
+          <t>1547</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1736
-</t>
+          <t>736</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
-</t>
+          <t>364</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
-</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1313
-</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>725</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">483
-</t>
+          <t>483</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11458
-</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12244
-</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2548,146 +2262,122 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
-</t>
+          <t>425</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">376
-</t>
+          <t>376</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2704,141 +2394,118 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2521
-</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
-</t>
+          <t>329</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1375
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8291
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1844
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2855,146 +2522,122 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3264
-</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
-</t>
+          <t>605</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">414
-</t>
+          <t>414</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3021,134 +2664,112 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3165,140 +2786,117 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0422
-</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
+          <t>490</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
-</t>
+          <t>366</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -3320,123 +2918,103 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5363
-</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">020
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2390
-</t>
+          <t>390</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
@@ -3446,14 +3024,12 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3470,141 +3046,118 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25175
-</t>
+          <t>25475</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1603
-</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
-</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
-</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
-</t>
+          <t>868</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>572</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">791
-</t>
+          <t>791</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
-</t>
+          <t>503</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2720
-</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">412
-</t>
+          <t>413</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1544
-</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr"/>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
-</t>
+          <t>366</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
-</t>
+          <t>829</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1872
-</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1305
-</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1688
-</t>
+          <t>688</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
-</t>
+          <t>428</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
-</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1274
-</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3621,141 +3174,118 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5095
-</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2946
-</t>
+          <t>546</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">374
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3772,146 +3302,122 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">455
-</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">400
-</t>
+          <t>400</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4573
-</t>
+          <t>453</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2212
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3928,146 +3434,122 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304
-</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1334
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2220
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4084,146 +3566,122 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5501
-</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">374
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4240,140 +3698,117 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6210
-</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5984
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">934
-</t>
+          <t>434</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -4395,122 +3830,102 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6249
-</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2383
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
-</t>
+          <t>413</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
-</t>
+          <t>335</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1471
-</t>
+          <t>471</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4520,20 +3935,17 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4550,128 +3962,107 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27819
-</t>
+          <t>27819</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1616
-</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">745
-</t>
+          <t>745</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
-</t>
+          <t>871</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">570
-</t>
+          <t>570</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2370
-</t>
+          <t>370</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1358
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2323
-</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>517</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
-</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>709</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>726</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1941
-</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
-</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr"/>
@@ -4682,8 +4073,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4700,130 +4090,109 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3364
-</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
-</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">465
-</t>
+          <t>465</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">388
-</t>
+          <t>388</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr"/>
@@ -4841,105 +4210,88 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086
-</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">338
-</t>
+          <t>338</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
-</t>
+          <t>390</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">336
-</t>
+          <t>336</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4949,14 +4301,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr"/>
@@ -4984,146 +4334,122 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4437
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
-</t>
+          <t>410</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14209
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5140,14 +4466,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3866
-</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -5157,128 +4481,107 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>522</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>500</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5295,50 +4598,42 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4339
-</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -5348,92 +4643,77 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1589
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5450,8 +4730,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3413
-</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -5461,129 +4740,108 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1048
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
-</t>
+          <t>540</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
-</t>
+          <t>348</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1806
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1466
-</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5600,141 +4858,118 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22166
-</t>
+          <t>22166</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1316
-</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1689
-</t>
+          <t>689</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
-</t>
+          <t>827</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
-</t>
+          <t>558</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>839</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1532
-</t>
+          <t>532</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">447
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24092
-</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3595
-</t>
+          <t>593</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
-</t>
+          <t>726</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1478
-</t>
+          <t>479</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1716
-</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1340
-</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11411
-</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>070</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr"/>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
-</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5751,141 +4986,118 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433
-</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>480</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">374
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5902,146 +5114,122 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59146
-</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11580
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1294
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
-</t>
+          <t>364</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6058,146 +5246,122 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
-</t>
+          <t>510</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
-</t>
+          <t>342</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12680
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3180
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6214,14 +5378,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5875
-</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -6231,128 +5393,107 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1530
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
-</t>
+          <t>490</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6369,80 +5510,67 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4811
-</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">392
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
-</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -6452,62 +5580,52 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13920
-</t>
+          <t>520</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6524,146 +5642,122 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2340
-</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>315</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6680,146 +5774,122 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580
-</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">092
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440
-</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12279
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2908
-</t>
+          <t>508</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6836,14 +5906,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23122
-</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
-</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -6853,111 +5921,93 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9108
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71949
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>350</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">523
-</t>
+          <t>523</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
-</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12029
-</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2265
-</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29084
-</t>
+          <t>584</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1780
-</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr"/>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1369
-</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1826
-</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1462
-</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2862
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1647
-</t>
+          <t>547</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr"/>
@@ -6976,141 +6026,122 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518
-</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4706
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
-</t>
+          <t>494</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1390
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23908
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2848
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">

--- a/results/05_transient_transcription_output/501/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/501/Midpoint_Excel_with_OCR_Results.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>124</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -1045,12 +1045,12 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>350</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>317</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>333</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>389</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>392</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2058,7 +2058,7 @@
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>262</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>268</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>362</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>41</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>125</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>165</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>76</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>375</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>404</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>67</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>96</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr"/>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>222</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>272</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>011</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>135</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>98</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>98</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>320</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3783,12 +3783,12 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>194</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>62</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>27819</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>358</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>318</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>62</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>273</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr"/>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>2437</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>322</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>300</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>340</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>202</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>358</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>393</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>670</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr"/>
@@ -5024,7 +5024,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
           <t>168</t>
@@ -5037,7 +5041,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>92</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -5067,7 +5071,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>303</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -5174,7 +5178,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>310</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5246,7 +5250,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5301,7 +5305,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -5433,7 +5437,7 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>102</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -5610,12 +5614,12 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>115</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5682,7 +5686,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -5742,7 +5746,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
@@ -5814,7 +5818,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -5829,12 +5833,12 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>440</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5859,7 +5863,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>193</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5906,7 +5910,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>33122</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5921,7 +5925,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>137</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5941,7 +5945,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>323</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -5956,12 +5960,12 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>270</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -6002,12 +6006,12 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>863</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr"/>
@@ -6031,7 +6035,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -6046,7 +6050,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>153</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -6081,7 +6085,7 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -6126,7 +6130,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>124</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
@@ -6136,7 +6140,7 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>311</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">

--- a/results/05_transient_transcription_output/501/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/501/Midpoint_Excel_with_OCR_Results.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>123</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -1045,12 +1045,12 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1178,7 +1178,7 @@
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>262</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>517</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>289</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>199</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>165</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2058,7 +2058,7 @@
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>480</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>768</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>562</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>725</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>554</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>154</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>78</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>175</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>98</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr"/>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>785</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>690</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>572</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>2720</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>099</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>320</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>520</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>104</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3783,12 +3783,12 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>94</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>434</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>27819</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>558</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>194</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>68</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>611</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2437</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>422</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>108</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>332</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>341</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>22166</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>558</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>070</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr"/>
@@ -5024,11 +5024,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
           <t>168</t>
@@ -5041,7 +5037,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>97</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -5138,7 +5134,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -5173,7 +5169,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>98</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -5305,7 +5301,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -5335,7 +5331,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>195</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -5437,7 +5433,7 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -5487,7 +5483,7 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5614,12 +5610,12 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>118</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5701,7 +5697,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -5778,7 +5774,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>580</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5833,7 +5829,7 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -5863,7 +5859,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>198</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5883,7 +5879,7 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>109</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5910,7 +5906,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>33122</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5935,7 +5931,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>719</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -5945,7 +5941,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>523</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -5960,12 +5956,12 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>650</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>578</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -5996,7 +5992,7 @@
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
@@ -6011,7 +6007,7 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>647</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr"/>
@@ -6070,7 +6066,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -6085,7 +6081,7 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -6130,7 +6126,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>144</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
@@ -6140,7 +6136,7 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>211</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
